--- a/EQUIPMENT_Data.xlsx
+++ b/EQUIPMENT_Data.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\@和泰資料\宇涵\@AI事務局\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4319295-DF61-4E19-A223-D9095CBD8CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A9BF7D-7F54-4D4E-87FA-313BA92C2B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B9AE4098-F0A1-4C76-B9D5-37F1BE2208A4}"/>
+    <workbookView xWindow="264" yWindow="0" windowWidth="22080" windowHeight="13680" xr2:uid="{B9AE4098-F0A1-4C76-B9D5-37F1BE2208A4}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_units" sheetId="1" r:id="rId1"/>
-    <sheet name="outdoor_units" sheetId="2" r:id="rId2"/>
-    <sheet name="indoor_units_SA only" sheetId="3" r:id="rId3"/>
-    <sheet name="outdoor_units_SA only" sheetId="4" r:id="rId4"/>
+    <sheet name="controller" sheetId="5" r:id="rId2"/>
+    <sheet name="outdoor_units" sheetId="2" r:id="rId3"/>
+    <sheet name="indoor_units_SA only" sheetId="3" r:id="rId4"/>
+    <sheet name="outdoor_units_SA only" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3120" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="615">
   <si>
     <t>資料型態</t>
   </si>
@@ -2029,15 +2030,346 @@
     <t>冷暖上吹型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>轉接小P版</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集控轉接基板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>室外機分歧頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遙控器型號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無線接收器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC084C45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>內建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRP067A42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRP072C42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRP980B42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KRP928BB2S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRP084C45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VRV / SA / RA</t>
+  </si>
+  <si>
+    <r>
+      <t>（必填）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> 區分系統，對應現有程式的判定。</t>
+    </r>
+  </si>
+  <si>
+    <t>橫綱V系列 / FXSQ</t>
+  </si>
+  <si>
+    <r>
+      <t>（必填）主鍵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，不可重複。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>（必填）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve"> 程式計算的核心冷房能力（kW）。</t>
+    </r>
+  </si>
+  <si>
+    <t>80 或 2.5馬力</t>
+  </si>
+  <si>
+    <t>最高靜壓（Pa），隱埋機型專屬，沒靜壓的填 0 或空著。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kRP928BB2S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRP072C42-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定價 (NT$)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[選填] 室內機定價。VRV 與 RA 家用多聯請填單機價；1對1 機型請留空或填 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[選填] 室外機定價。1對1 請填「室外機+室內機」合併總價；VRV/多聯請填室外機單價</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商用 1對1 皆為整組報價，此分頁各欄可直接留空或填 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商用 1對1（如 RZF71、RZAC71、RZF140 等），填入商用 1對1（室內機+室外機）整組合併定價。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有線遙控器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無線遙控器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2MXP85ZVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>395×930×350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC1E63R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC4C65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC4C62-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC7M634F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC7M675</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC7EA63W9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC7M530W</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BRC7M65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中控制器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCS301BA61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中ON-OFF控制器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央集中控制器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCS302CA61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCS303A61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DST301BA61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家用集中控制器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>預定時程控制器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTP401A61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTP401A63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中央集控外接監控基板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCS302A52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC集中控制器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC集中控制器電源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCM601B51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGE601A52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITM擴充卡1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGE601A53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITM擴充卡插槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCM009A51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCM007A51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITM WEB網路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>網路接伶俐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTA116A51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modbus 介面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BACnet 介面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITM BACnet協定軟體</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMS502B51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAM411B51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BACnet 擴充組</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCPA01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伶俐用轉接器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCPF01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伶俐智控管理器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2089,8 +2421,31 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2103,8 +2458,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2179,13 +2540,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2258,6 +2645,126 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2276,9 +2783,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2316,7 +2823,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2422,7 +2929,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2564,7 +3071,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2572,7 +3079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E6F3F9-85F0-48DB-9A66-1B3BA6E48A6F}">
-  <dimension ref="A1:GL12"/>
+  <dimension ref="A1:GL19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.109375" style="2" customWidth="1"/>
@@ -2580,226 +3087,228 @@
     <col min="3" max="3" width="14.6640625" style="6" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="41.44140625" style="2" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" style="6" customWidth="1"/>
-    <col min="6" max="193" width="10.6640625" style="2" customWidth="1"/>
+    <col min="6" max="87" width="10.6640625" style="2" customWidth="1"/>
+    <col min="88" max="88" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="89" max="193" width="10.6640625" style="2" customWidth="1"/>
     <col min="194" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:194" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:194" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
-      <c r="AB1" s="4"/>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="4"/>
-      <c r="AH1" s="4"/>
-      <c r="AI1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
-      <c r="AL1" s="4"/>
-      <c r="AM1" s="4"/>
-      <c r="AN1" s="4"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="4"/>
-      <c r="AQ1" s="4"/>
-      <c r="AR1" s="4"/>
-      <c r="AS1" s="4"/>
-      <c r="AT1" s="4"/>
-      <c r="AU1" s="4"/>
-      <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-      <c r="CN1" s="4"/>
-      <c r="CO1" s="4"/>
-      <c r="CP1" s="4"/>
-      <c r="CQ1" s="4"/>
-      <c r="CR1" s="4"/>
-      <c r="CS1" s="4"/>
-      <c r="CT1" s="4"/>
-      <c r="CU1" s="4"/>
-      <c r="CV1" s="4"/>
-      <c r="CW1" s="4"/>
-      <c r="CX1" s="4"/>
-      <c r="CY1" s="4"/>
-      <c r="CZ1" s="4"/>
-      <c r="DA1" s="4"/>
-      <c r="DB1" s="4"/>
-      <c r="DC1" s="4"/>
-      <c r="DD1" s="4"/>
-      <c r="DE1" s="4"/>
-      <c r="DF1" s="4"/>
-      <c r="DG1" s="4"/>
-      <c r="DH1" s="4"/>
-      <c r="DI1" s="4"/>
-      <c r="DJ1" s="4"/>
-      <c r="DK1" s="4"/>
-      <c r="DL1" s="4"/>
-      <c r="DM1" s="4"/>
-      <c r="DN1" s="4"/>
-      <c r="DO1" s="4"/>
-      <c r="DP1" s="4"/>
-      <c r="DQ1" s="4"/>
-      <c r="DR1" s="4"/>
-      <c r="DS1" s="4"/>
-      <c r="DT1" s="4"/>
-      <c r="DU1" s="4"/>
-      <c r="DV1" s="4"/>
-      <c r="DW1" s="4"/>
-      <c r="DX1" s="4"/>
-      <c r="DY1" s="4"/>
-      <c r="DZ1" s="4"/>
-      <c r="EA1" s="4"/>
-      <c r="EB1" s="4"/>
-      <c r="EC1" s="4"/>
-      <c r="ED1" s="4"/>
-      <c r="EE1" s="4"/>
-      <c r="EF1" s="4"/>
-      <c r="EG1" s="4"/>
-      <c r="EH1" s="4"/>
-      <c r="EI1" s="4"/>
-      <c r="EJ1" s="4"/>
-      <c r="EK1" s="4"/>
-      <c r="EL1" s="4"/>
-      <c r="EM1" s="4"/>
-      <c r="EN1" s="4"/>
-      <c r="EO1" s="4"/>
-      <c r="EP1" s="4"/>
-      <c r="EQ1" s="4"/>
-      <c r="ER1" s="4"/>
-      <c r="ES1" s="4"/>
-      <c r="ET1" s="4"/>
-      <c r="EU1" s="4"/>
-      <c r="EV1" s="4"/>
-      <c r="EW1" s="4"/>
-      <c r="EX1" s="4"/>
-      <c r="EY1" s="4"/>
-      <c r="EZ1" s="4"/>
-      <c r="FA1" s="4"/>
-      <c r="FB1" s="4"/>
-      <c r="FC1" s="4"/>
-      <c r="FD1" s="4"/>
-      <c r="FE1" s="4"/>
-      <c r="FF1" s="4"/>
-      <c r="FG1" s="4"/>
-      <c r="FH1" s="4"/>
-      <c r="FI1" s="4"/>
-      <c r="FJ1" s="4"/>
-      <c r="FK1" s="4"/>
-      <c r="FL1" s="4"/>
-      <c r="FM1" s="4"/>
-      <c r="FN1" s="4"/>
-      <c r="FO1" s="4"/>
-      <c r="FP1" s="4"/>
-      <c r="FQ1" s="4"/>
-      <c r="FR1" s="4"/>
-      <c r="FS1" s="4"/>
-      <c r="FT1" s="4"/>
-      <c r="FU1" s="4"/>
-      <c r="FV1" s="4"/>
-      <c r="FW1" s="4"/>
-      <c r="FX1" s="4"/>
-      <c r="FY1" s="4"/>
-      <c r="FZ1" s="4"/>
-      <c r="GA1" s="4"/>
-      <c r="GB1" s="4"/>
-      <c r="GC1" s="4"/>
-      <c r="GD1" s="4"/>
-      <c r="GE1" s="4"/>
-      <c r="GF1" s="4"/>
-      <c r="GG1" s="4"/>
-      <c r="GH1" s="4"/>
-      <c r="GI1" s="4"/>
-      <c r="GJ1" s="4"/>
-      <c r="GK1" s="4"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+      <c r="AZ1" s="34"/>
+      <c r="BA1" s="34"/>
+      <c r="BB1" s="34"/>
+      <c r="BC1" s="34"/>
+      <c r="BD1" s="34"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
+      <c r="BJ1" s="34"/>
+      <c r="BK1" s="34"/>
+      <c r="BL1" s="34"/>
+      <c r="BM1" s="34"/>
+      <c r="BN1" s="34"/>
+      <c r="BO1" s="34"/>
+      <c r="BP1" s="34"/>
+      <c r="BQ1" s="34"/>
+      <c r="BR1" s="34"/>
+      <c r="BS1" s="34"/>
+      <c r="BT1" s="34"/>
+      <c r="BU1" s="34"/>
+      <c r="BV1" s="34"/>
+      <c r="BW1" s="34"/>
+      <c r="BX1" s="34"/>
+      <c r="BY1" s="34"/>
+      <c r="BZ1" s="34"/>
+      <c r="CA1" s="34"/>
+      <c r="CB1" s="34"/>
+      <c r="CC1" s="34"/>
+      <c r="CD1" s="34"/>
+      <c r="CE1" s="34"/>
+      <c r="CF1" s="34"/>
+      <c r="CG1" s="34"/>
+      <c r="CH1" s="34"/>
+      <c r="CI1" s="34"/>
+      <c r="CJ1" s="34"/>
+      <c r="CK1" s="34"/>
+      <c r="CL1" s="34"/>
+      <c r="CM1" s="34"/>
+      <c r="CN1" s="34"/>
+      <c r="CO1" s="34"/>
+      <c r="CP1" s="34"/>
+      <c r="CQ1" s="34"/>
+      <c r="CR1" s="34"/>
+      <c r="CS1" s="34"/>
+      <c r="CT1" s="34"/>
+      <c r="CU1" s="34"/>
+      <c r="CV1" s="34"/>
+      <c r="CW1" s="34"/>
+      <c r="CX1" s="34"/>
+      <c r="CY1" s="34"/>
+      <c r="CZ1" s="34"/>
+      <c r="DA1" s="34"/>
+      <c r="DB1" s="34"/>
+      <c r="DC1" s="34"/>
+      <c r="DD1" s="34"/>
+      <c r="DE1" s="34"/>
+      <c r="DF1" s="34"/>
+      <c r="DG1" s="34"/>
+      <c r="DH1" s="34"/>
+      <c r="DI1" s="34"/>
+      <c r="DJ1" s="34"/>
+      <c r="DK1" s="34"/>
+      <c r="DL1" s="34"/>
+      <c r="DM1" s="34"/>
+      <c r="DN1" s="34"/>
+      <c r="DO1" s="34"/>
+      <c r="DP1" s="34"/>
+      <c r="DQ1" s="34"/>
+      <c r="DR1" s="34"/>
+      <c r="DS1" s="34"/>
+      <c r="DT1" s="34"/>
+      <c r="DU1" s="34"/>
+      <c r="DV1" s="34"/>
+      <c r="DW1" s="34"/>
+      <c r="DX1" s="34"/>
+      <c r="DY1" s="34"/>
+      <c r="DZ1" s="34"/>
+      <c r="EA1" s="34"/>
+      <c r="EB1" s="34"/>
+      <c r="EC1" s="34"/>
+      <c r="ED1" s="34"/>
+      <c r="EE1" s="34"/>
+      <c r="EF1" s="34"/>
+      <c r="EG1" s="34"/>
+      <c r="EH1" s="34"/>
+      <c r="EI1" s="34"/>
+      <c r="EJ1" s="34"/>
+      <c r="EK1" s="34"/>
+      <c r="EL1" s="34"/>
+      <c r="EM1" s="34"/>
+      <c r="EN1" s="34"/>
+      <c r="EO1" s="34"/>
+      <c r="EP1" s="34"/>
+      <c r="EQ1" s="34"/>
+      <c r="ER1" s="34"/>
+      <c r="ES1" s="34"/>
+      <c r="ET1" s="34"/>
+      <c r="EU1" s="34"/>
+      <c r="EV1" s="34"/>
+      <c r="EW1" s="34"/>
+      <c r="EX1" s="34"/>
+      <c r="EY1" s="34"/>
+      <c r="EZ1" s="34"/>
+      <c r="FA1" s="34"/>
+      <c r="FB1" s="34"/>
+      <c r="FC1" s="34"/>
+      <c r="FD1" s="34"/>
+      <c r="FE1" s="34"/>
+      <c r="FF1" s="34"/>
+      <c r="FG1" s="34"/>
+      <c r="FH1" s="34"/>
+      <c r="FI1" s="34"/>
+      <c r="FJ1" s="34"/>
+      <c r="FK1" s="34"/>
+      <c r="FL1" s="34"/>
+      <c r="FM1" s="34"/>
+      <c r="FN1" s="34"/>
+      <c r="FO1" s="34"/>
+      <c r="FP1" s="34"/>
+      <c r="FQ1" s="34"/>
+      <c r="FR1" s="34"/>
+      <c r="FS1" s="34"/>
+      <c r="FT1" s="34"/>
+      <c r="FU1" s="34"/>
+      <c r="FV1" s="34"/>
+      <c r="FW1" s="34"/>
+      <c r="FX1" s="34"/>
+      <c r="FY1" s="34"/>
+      <c r="FZ1" s="34"/>
+      <c r="GA1" s="34"/>
+      <c r="GB1" s="34"/>
+      <c r="GC1" s="34"/>
+      <c r="GD1" s="34"/>
+      <c r="GE1" s="34"/>
+      <c r="GF1" s="34"/>
+      <c r="GG1" s="34"/>
+      <c r="GH1" s="34"/>
+      <c r="GI1" s="34"/>
+      <c r="GJ1" s="34"/>
+      <c r="GK1" s="34"/>
       <c r="GL1" s="4"/>
     </row>
-    <row r="2" spans="1:194" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:194" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>17</v>
+        <v>552</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>553</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>218</v>
@@ -3370,17 +3879,17 @@
       </c>
       <c r="GL2" s="5"/>
     </row>
-    <row r="3" spans="1:194" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:194" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="D3" s="37" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -3953,17 +4462,17 @@
       <c r="GL3" s="5"/>
     </row>
     <row r="4" spans="1:194" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>19</v>
+      <c r="D4" s="36" t="s">
+        <v>555</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>236</v>
@@ -4534,18 +5043,18 @@
       </c>
       <c r="GL4" s="5"/>
     </row>
-    <row r="5" spans="1:194" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:194" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="5">
         <v>9</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>20</v>
+      <c r="D5" s="36" t="s">
+        <v>556</v>
       </c>
       <c r="E5" s="20">
         <v>2.2000000000000002</v>
@@ -5116,17 +5625,17 @@
       </c>
       <c r="GL5" s="5"/>
     </row>
-    <row r="6" spans="1:194" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:194" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
         <v>474</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="35" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -5698,17 +6207,17 @@
       </c>
       <c r="GL6" s="5"/>
     </row>
-    <row r="7" spans="1:194" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:194" ht="24.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="32" t="s">
         <v>475</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="37" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -6280,17 +6789,17 @@
       </c>
       <c r="GL7" s="5"/>
     </row>
-    <row r="8" spans="1:194" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:194" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="5">
         <v>0.12</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="37" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -6862,17 +7371,17 @@
       </c>
       <c r="GL8" s="5"/>
     </row>
-    <row r="9" spans="1:194" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:194" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="5">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="37" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -7444,18 +7953,18 @@
       </c>
       <c r="GL9" s="5"/>
     </row>
-    <row r="10" spans="1:194" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:194" ht="24.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="35" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5">
         <v>50</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>22</v>
+      <c r="D10" s="37" t="s">
+        <v>558</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>414</v>
@@ -8026,17 +8535,17 @@
       </c>
       <c r="GL10" s="5"/>
     </row>
-    <row r="11" spans="1:194" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:194" ht="24.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="35" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="37" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -8608,587 +9117,2900 @@
       </c>
       <c r="GL11" s="5"/>
     </row>
-    <row r="12" spans="1:194" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:194" ht="24.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="37" t="s">
         <v>466</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="R12" s="9" t="s">
+      <c r="R12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="S12" s="9" t="s">
+      <c r="S12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="T12" s="9" t="s">
+      <c r="T12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="U12" s="9" t="s">
+      <c r="U12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="V12" s="9" t="s">
+      <c r="V12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="W12" s="9" t="s">
+      <c r="W12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="X12" s="9" t="s">
+      <c r="X12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="Y12" s="9" t="s">
+      <c r="Y12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="Z12" s="9" t="s">
+      <c r="Z12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AA12" s="9" t="s">
+      <c r="AA12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AB12" s="9" t="s">
+      <c r="AB12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AC12" s="9" t="s">
+      <c r="AC12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AD12" s="9" t="s">
+      <c r="AD12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AE12" s="9" t="s">
+      <c r="AE12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AF12" s="9" t="s">
+      <c r="AF12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AG12" s="9" t="s">
+      <c r="AG12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AH12" s="9" t="s">
+      <c r="AH12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AI12" s="9" t="s">
+      <c r="AI12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AJ12" s="9" t="s">
+      <c r="AJ12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AK12" s="9" t="s">
+      <c r="AK12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AL12" s="9" t="s">
+      <c r="AL12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AM12" s="9" t="s">
+      <c r="AM12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AN12" s="9" t="s">
+      <c r="AN12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AO12" s="9" t="s">
+      <c r="AO12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AP12" s="9" t="s">
+      <c r="AP12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AQ12" s="9" t="s">
+      <c r="AQ12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AR12" s="9" t="s">
+      <c r="AR12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AS12" s="9" t="s">
+      <c r="AS12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AT12" s="9" t="s">
+      <c r="AT12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AU12" s="9" t="s">
+      <c r="AU12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AV12" s="9" t="s">
+      <c r="AV12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AW12" s="9" t="s">
+      <c r="AW12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AX12" s="9" t="s">
+      <c r="AX12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AY12" s="9" t="s">
+      <c r="AY12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="AZ12" s="9" t="s">
+      <c r="AZ12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BA12" s="9" t="s">
+      <c r="BA12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BB12" s="9" t="s">
+      <c r="BB12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BC12" s="9" t="s">
+      <c r="BC12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BD12" s="9" t="s">
+      <c r="BD12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BE12" s="9" t="s">
+      <c r="BE12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BF12" s="9" t="s">
+      <c r="BF12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BG12" s="9" t="s">
+      <c r="BG12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BH12" s="9" t="s">
+      <c r="BH12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BI12" s="9" t="s">
+      <c r="BI12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BJ12" s="9" t="s">
+      <c r="BJ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BK12" s="9" t="s">
+      <c r="BK12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BL12" s="9" t="s">
+      <c r="BL12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BM12" s="9" t="s">
+      <c r="BM12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BN12" s="9" t="s">
+      <c r="BN12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BO12" s="9" t="s">
+      <c r="BO12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BP12" s="9" t="s">
+      <c r="BP12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BQ12" s="9" t="s">
+      <c r="BQ12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BR12" s="9" t="s">
+      <c r="BR12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BS12" s="9" t="s">
+      <c r="BS12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BT12" s="9" t="s">
+      <c r="BT12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BU12" s="9" t="s">
+      <c r="BU12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="BV12" s="9" t="s">
+      <c r="BV12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BW12" s="9" t="s">
+      <c r="BW12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BX12" s="9" t="s">
+      <c r="BX12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BY12" s="9" t="s">
+      <c r="BY12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="BZ12" s="9" t="s">
+      <c r="BZ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CA12" s="9" t="s">
+      <c r="CA12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CB12" s="9" t="s">
+      <c r="CB12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CC12" s="9" t="s">
+      <c r="CC12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CD12" s="9" t="s">
+      <c r="CD12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CE12" s="9" t="s">
+      <c r="CE12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CF12" s="9" t="s">
+      <c r="CF12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CG12" s="9" t="s">
+      <c r="CG12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CH12" s="9" t="s">
+      <c r="CH12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CI12" s="9" t="s">
+      <c r="CI12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="CJ12" s="9" t="s">
+      <c r="CJ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CK12" s="9" t="s">
+      <c r="CK12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CL12" s="9" t="s">
+      <c r="CL12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CM12" s="9" t="s">
+      <c r="CM12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CN12" s="9" t="s">
+      <c r="CN12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CO12" s="9" t="s">
+      <c r="CO12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CP12" s="9" t="s">
+      <c r="CP12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CQ12" s="9" t="s">
+      <c r="CQ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CR12" s="9" t="s">
+      <c r="CR12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CS12" s="9" t="s">
+      <c r="CS12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CT12" s="9" t="s">
+      <c r="CT12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CU12" s="9" t="s">
+      <c r="CU12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CV12" s="9" t="s">
+      <c r="CV12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CW12" s="9" t="s">
+      <c r="CW12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CX12" s="9" t="s">
+      <c r="CX12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CY12" s="9" t="s">
+      <c r="CY12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="CZ12" s="9" t="s">
+      <c r="CZ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DA12" s="9" t="s">
+      <c r="DA12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DB12" s="9" t="s">
+      <c r="DB12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DC12" s="9" t="s">
+      <c r="DC12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DD12" s="9" t="s">
+      <c r="DD12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DE12" s="9" t="s">
+      <c r="DE12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DF12" s="9" t="s">
+      <c r="DF12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DG12" s="9" t="s">
+      <c r="DG12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DH12" s="9" t="s">
+      <c r="DH12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DI12" s="9" t="s">
+      <c r="DI12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DJ12" s="9" t="s">
+      <c r="DJ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DK12" s="9" t="s">
+      <c r="DK12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DL12" s="9" t="s">
+      <c r="DL12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DM12" s="9" t="s">
+      <c r="DM12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DN12" s="9" t="s">
+      <c r="DN12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DO12" s="9" t="s">
+      <c r="DO12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DP12" s="9" t="s">
+      <c r="DP12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DQ12" s="9" t="s">
+      <c r="DQ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DR12" s="9" t="s">
+      <c r="DR12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DS12" s="9" t="s">
+      <c r="DS12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DT12" s="9" t="s">
+      <c r="DT12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DU12" s="9" t="s">
+      <c r="DU12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DV12" s="9" t="s">
+      <c r="DV12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DW12" s="9" t="s">
+      <c r="DW12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DX12" s="9" t="s">
+      <c r="DX12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DY12" s="9" t="s">
+      <c r="DY12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="DZ12" s="9" t="s">
+      <c r="DZ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="EA12" s="9" t="s">
+      <c r="EA12" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="EB12" s="9" t="s">
+      <c r="EB12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EC12" s="9" t="s">
+      <c r="EC12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="ED12" s="9" t="s">
+      <c r="ED12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EE12" s="9" t="s">
+      <c r="EE12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EF12" s="9" t="s">
+      <c r="EF12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EG12" s="9" t="s">
+      <c r="EG12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EH12" s="9" t="s">
+      <c r="EH12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EI12" s="9" t="s">
+      <c r="EI12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EJ12" s="9" t="s">
+      <c r="EJ12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EK12" s="9" t="s">
+      <c r="EK12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EL12" s="9" t="s">
+      <c r="EL12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EM12" s="9" t="s">
+      <c r="EM12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EN12" s="9" t="s">
+      <c r="EN12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EO12" s="9" t="s">
+      <c r="EO12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EP12" s="9" t="s">
+      <c r="EP12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="EQ12" s="9" t="s">
+      <c r="EQ12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="ER12" s="9" t="s">
+      <c r="ER12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="ES12" s="9" t="s">
+      <c r="ES12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="ET12" s="9" t="s">
+      <c r="ET12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="EU12" s="9" t="s">
+      <c r="EU12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="EV12" s="9" t="s">
+      <c r="EV12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="EW12" s="9" t="s">
+      <c r="EW12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="EX12" s="9" t="s">
+      <c r="EX12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="EY12" s="9" t="s">
+      <c r="EY12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="EZ12" s="9" t="s">
+      <c r="EZ12" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="FA12" s="9" t="s">
+      <c r="FA12" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="FB12" s="9" t="s">
+      <c r="FB12" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="FC12" s="9" t="s">
+      <c r="FC12" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="FD12" s="9" t="s">
+      <c r="FD12" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="FE12" s="9" t="s">
+      <c r="FE12" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="FF12" s="9" t="s">
+      <c r="FF12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FG12" s="9" t="s">
+      <c r="FG12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FH12" s="9" t="s">
+      <c r="FH12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FI12" s="9" t="s">
+      <c r="FI12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FJ12" s="9" t="s">
+      <c r="FJ12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FK12" s="9" t="s">
+      <c r="FK12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FL12" s="9" t="s">
+      <c r="FL12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FM12" s="9" t="s">
+      <c r="FM12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FN12" s="9" t="s">
+      <c r="FN12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FO12" s="9" t="s">
+      <c r="FO12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FP12" s="9" t="s">
+      <c r="FP12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FQ12" s="9" t="s">
+      <c r="FQ12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FR12" s="9" t="s">
+      <c r="FR12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FS12" s="9" t="s">
+      <c r="FS12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FT12" s="9" t="s">
+      <c r="FT12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FU12" s="9" t="s">
+      <c r="FU12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FV12" s="9" t="s">
+      <c r="FV12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FW12" s="9" t="s">
+      <c r="FW12" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="FX12" s="9" t="s">
+      <c r="FX12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="FY12" s="9" t="s">
+      <c r="FY12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="FZ12" s="9" t="s">
+      <c r="FZ12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="GA12" s="9" t="s">
+      <c r="GA12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="GB12" s="9" t="s">
+      <c r="GB12" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="GC12" s="9" t="s">
+      <c r="GC12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GD12" s="9" t="s">
+      <c r="GD12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GE12" s="9" t="s">
+      <c r="GE12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GF12" s="9" t="s">
+      <c r="GF12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GG12" s="9" t="s">
+      <c r="GG12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GH12" s="9" t="s">
+      <c r="GH12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GI12" s="9" t="s">
+      <c r="GI12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GJ12" s="9" t="s">
+      <c r="GJ12" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="GK12" s="9" t="s">
+      <c r="GK12" s="5" t="s">
         <v>467</v>
       </c>
       <c r="GL12" s="9"/>
+    </row>
+    <row r="13" spans="1:194" ht="16.2" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="40" t="s">
+        <v>543</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="40"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
+      <c r="AM13" s="40"/>
+      <c r="AN13" s="40"/>
+      <c r="AO13" s="40"/>
+      <c r="AP13" s="40"/>
+      <c r="AQ13" s="40"/>
+      <c r="AR13" s="40"/>
+      <c r="AS13" s="40"/>
+      <c r="AT13" s="40"/>
+      <c r="AU13" s="40"/>
+      <c r="AV13" s="40"/>
+      <c r="AW13" s="40"/>
+      <c r="AX13" s="40"/>
+      <c r="AY13" s="40"/>
+      <c r="AZ13" s="40"/>
+      <c r="BA13" s="40"/>
+      <c r="BB13" s="40"/>
+      <c r="BC13" s="40"/>
+      <c r="BD13" s="40"/>
+      <c r="BE13" s="40"/>
+      <c r="BF13" s="40"/>
+      <c r="BG13" s="40"/>
+      <c r="BH13" s="40"/>
+      <c r="BI13" s="40"/>
+      <c r="BJ13" s="40"/>
+      <c r="BK13" s="40"/>
+      <c r="BL13" s="40"/>
+      <c r="BM13" s="40"/>
+      <c r="BN13" s="40"/>
+      <c r="BO13" s="40"/>
+      <c r="BP13" s="40"/>
+      <c r="BQ13" s="40"/>
+      <c r="BR13" s="40"/>
+      <c r="BS13" s="40"/>
+      <c r="BT13" s="40"/>
+      <c r="BU13" s="40"/>
+      <c r="BV13" s="40"/>
+      <c r="BW13" s="40" t="s">
+        <v>559</v>
+      </c>
+      <c r="BX13" s="40"/>
+      <c r="BY13" s="40"/>
+      <c r="BZ13" s="40"/>
+      <c r="CA13" s="40"/>
+      <c r="CB13" s="40"/>
+      <c r="CC13" s="40"/>
+      <c r="CD13" s="40"/>
+      <c r="CE13" s="40"/>
+      <c r="CF13" s="40"/>
+      <c r="CG13" s="40"/>
+      <c r="CH13" s="40"/>
+      <c r="CI13" s="40"/>
+      <c r="CJ13" s="40"/>
+      <c r="CK13" s="40"/>
+      <c r="CL13" s="40"/>
+      <c r="CM13" s="40"/>
+      <c r="CN13" s="40"/>
+      <c r="CO13" s="40"/>
+      <c r="CP13" s="40"/>
+      <c r="CQ13" s="40"/>
+      <c r="CR13" s="40"/>
+      <c r="CS13" s="40"/>
+      <c r="CT13" s="40"/>
+      <c r="CU13" s="40"/>
+      <c r="CV13" s="40"/>
+      <c r="CW13" s="40"/>
+      <c r="CX13" s="40"/>
+      <c r="CY13" s="40"/>
+      <c r="CZ13" s="40"/>
+      <c r="DA13" s="40"/>
+      <c r="DB13" s="40"/>
+      <c r="DC13" s="40"/>
+      <c r="DD13" s="40"/>
+      <c r="DE13" s="40"/>
+      <c r="DF13" s="40"/>
+      <c r="DG13" s="40"/>
+      <c r="DH13" s="40"/>
+      <c r="DI13" s="40"/>
+      <c r="DJ13" s="40"/>
+      <c r="DK13" s="40"/>
+      <c r="DL13" s="40"/>
+      <c r="DM13" s="40"/>
+      <c r="DN13" s="40"/>
+      <c r="DO13" s="40"/>
+      <c r="DP13" s="40"/>
+      <c r="DQ13" s="40"/>
+      <c r="DR13" s="40"/>
+      <c r="DS13" s="40"/>
+      <c r="DT13" s="40"/>
+      <c r="DU13" s="40"/>
+      <c r="DV13" s="40"/>
+      <c r="DW13" s="40"/>
+      <c r="DX13" s="40"/>
+      <c r="DY13" s="40"/>
+      <c r="DZ13" s="40"/>
+      <c r="EA13" s="40"/>
+      <c r="EB13" s="40"/>
+      <c r="EC13" s="40"/>
+      <c r="ED13" s="40"/>
+      <c r="EE13" s="40"/>
+      <c r="EF13" s="40"/>
+      <c r="EG13" s="40"/>
+      <c r="EH13" s="40"/>
+      <c r="EI13" s="40"/>
+      <c r="EJ13" s="40"/>
+      <c r="EK13" s="40"/>
+      <c r="EL13" s="40"/>
+      <c r="EM13" s="40"/>
+      <c r="EN13" s="40"/>
+      <c r="EO13" s="40"/>
+      <c r="EP13" s="40"/>
+      <c r="EQ13" s="40"/>
+      <c r="ER13" s="40"/>
+      <c r="ES13" s="40"/>
+      <c r="ET13" s="40"/>
+      <c r="EU13" s="40"/>
+      <c r="EV13" s="40"/>
+      <c r="EW13" s="40"/>
+      <c r="EX13" s="40"/>
+      <c r="EY13" s="40"/>
+      <c r="EZ13" s="40"/>
+      <c r="FA13" s="40"/>
+      <c r="FB13" s="40"/>
+      <c r="FC13" s="40"/>
+      <c r="FD13" s="40"/>
+      <c r="FE13" s="40"/>
+      <c r="FF13" s="40"/>
+      <c r="FG13" s="40"/>
+      <c r="FH13" s="40"/>
+      <c r="FI13" s="40"/>
+      <c r="FJ13" s="40"/>
+      <c r="FK13" s="40"/>
+      <c r="FL13" s="40"/>
+      <c r="FM13" s="40"/>
+      <c r="FN13" s="40"/>
+      <c r="FO13" s="40"/>
+      <c r="FP13" s="40"/>
+      <c r="FQ13" s="40"/>
+      <c r="FR13" s="40"/>
+      <c r="FS13" s="40"/>
+      <c r="FT13" s="40"/>
+      <c r="FU13" s="40"/>
+      <c r="FV13" s="40"/>
+      <c r="FW13" s="40"/>
+      <c r="FX13" s="40"/>
+      <c r="FY13" s="40"/>
+      <c r="FZ13" s="40"/>
+      <c r="GA13" s="40"/>
+      <c r="GB13" s="40"/>
+      <c r="GC13" s="40"/>
+      <c r="GD13" s="40"/>
+      <c r="GE13" s="40"/>
+      <c r="GF13" s="40"/>
+      <c r="GG13" s="40"/>
+      <c r="GH13" s="40"/>
+      <c r="GI13" s="40"/>
+      <c r="GJ13" s="40"/>
+      <c r="GK13" s="40"/>
+    </row>
+    <row r="14" spans="1:194" customFormat="1" ht="16.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="39" t="s">
+        <v>540</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="43"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="T14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="U14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="W14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="X14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AE14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AF14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AG14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AH14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AI14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AJ14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AK14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AL14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AM14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AN14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AO14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AP14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AQ14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AR14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AS14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AT14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AU14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AV14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AW14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AX14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="AY14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="AZ14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="BA14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="BB14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="BC14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="BD14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="BE14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="BF14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BH14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BI14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BJ14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BK14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BL14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BM14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BN14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BO14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BP14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BQ14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BR14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BS14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BT14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BU14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BV14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BW14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BX14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BY14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BZ14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="CA14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="CB14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="CC14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="CD14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="CE14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="CF14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="CG14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="CH14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="CI14" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="CJ14" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="CK14" s="44"/>
+      <c r="CL14" s="44"/>
+      <c r="CM14" s="44"/>
+      <c r="CN14" s="44"/>
+      <c r="CO14" s="44"/>
+      <c r="CP14" s="44"/>
+      <c r="CQ14" s="44"/>
+      <c r="CR14" s="44"/>
+      <c r="CS14" s="44"/>
+      <c r="CT14" s="44"/>
+      <c r="CU14" s="44"/>
+      <c r="CV14" s="44"/>
+      <c r="CW14" s="44"/>
+      <c r="CX14" s="44"/>
+      <c r="CY14" s="44"/>
+      <c r="CZ14" s="44"/>
+      <c r="DA14" s="44"/>
+      <c r="DB14" s="44"/>
+      <c r="DC14" s="44"/>
+      <c r="DD14" s="44"/>
+      <c r="DE14" s="44"/>
+      <c r="DF14" s="44"/>
+      <c r="DG14" s="44"/>
+      <c r="DH14" s="44"/>
+      <c r="DI14" s="44"/>
+      <c r="DJ14" s="44"/>
+      <c r="DK14" s="44"/>
+      <c r="DL14" s="44"/>
+      <c r="DM14" s="44"/>
+      <c r="DN14" s="44"/>
+      <c r="DO14" s="44"/>
+      <c r="DP14" s="44"/>
+      <c r="DQ14" s="44"/>
+      <c r="DR14" s="44"/>
+      <c r="DS14" s="44"/>
+      <c r="DT14" s="44"/>
+      <c r="DU14" s="44"/>
+      <c r="DV14" s="44"/>
+      <c r="DW14" s="44"/>
+      <c r="DX14" s="44"/>
+      <c r="DY14" s="44"/>
+      <c r="DZ14" s="44"/>
+      <c r="EA14" s="44"/>
+      <c r="EB14" s="44"/>
+      <c r="EC14" s="44"/>
+      <c r="ED14" s="44"/>
+      <c r="EE14" s="44"/>
+      <c r="EF14" s="44"/>
+      <c r="EG14" s="44"/>
+      <c r="EH14" s="44"/>
+      <c r="EI14" s="44"/>
+      <c r="EJ14" s="44"/>
+      <c r="EK14" s="44"/>
+      <c r="EL14" s="44"/>
+      <c r="EM14" s="44"/>
+      <c r="EN14" s="44"/>
+      <c r="EO14" s="44"/>
+      <c r="EP14" s="44"/>
+      <c r="EQ14" s="44"/>
+      <c r="ER14" s="44"/>
+      <c r="ES14" s="44"/>
+      <c r="ET14" s="44"/>
+      <c r="EU14" s="44"/>
+      <c r="EV14" s="44"/>
+      <c r="EW14" s="44"/>
+      <c r="EX14" s="44"/>
+      <c r="EY14" s="44"/>
+      <c r="EZ14" s="44"/>
+      <c r="FA14" s="44"/>
+      <c r="FB14" s="44"/>
+      <c r="FC14" s="44"/>
+      <c r="FD14" s="44"/>
+      <c r="FE14" s="44"/>
+      <c r="FF14" s="44"/>
+      <c r="FG14" s="44"/>
+      <c r="FH14" s="44"/>
+      <c r="FI14" s="44"/>
+      <c r="FJ14" s="44"/>
+      <c r="FK14" s="44"/>
+      <c r="FL14" s="44"/>
+      <c r="FM14" s="44"/>
+      <c r="FN14" s="44"/>
+      <c r="FO14" s="44"/>
+      <c r="FP14" s="44"/>
+      <c r="FQ14" s="44"/>
+      <c r="FR14" s="44"/>
+      <c r="FS14" s="44"/>
+      <c r="FT14" s="44"/>
+      <c r="FU14" s="44"/>
+      <c r="FV14" s="44"/>
+      <c r="FW14" s="44"/>
+      <c r="FX14" s="44"/>
+      <c r="FY14" s="44"/>
+      <c r="FZ14" s="44"/>
+      <c r="GA14" s="44"/>
+      <c r="GB14" s="44"/>
+      <c r="GC14" s="44"/>
+      <c r="GD14" s="44"/>
+      <c r="GE14" s="44"/>
+      <c r="GF14" s="44"/>
+      <c r="GG14" s="44"/>
+      <c r="GH14" s="44"/>
+      <c r="GI14" s="44"/>
+      <c r="GJ14" s="44"/>
+      <c r="GK14" s="44"/>
+    </row>
+    <row r="15" spans="1:194" customFormat="1" ht="16.8" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="I15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="J15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="L15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="N15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="O15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="P15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="R15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="S15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="T15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="U15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="V15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="W15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="X15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="Y15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="Z15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="AA15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="AB15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="AC15" s="44" t="s">
+        <v>545</v>
+      </c>
+      <c r="AD15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AE15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AF15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AG15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AH15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AI15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AJ15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AK15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AL15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AM15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AN15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AO15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AP15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AQ15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AR15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AS15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AT15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AU15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AV15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AW15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AX15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AY15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="AZ15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BA15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BB15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BC15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BD15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BE15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BF15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BG15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BH15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BI15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BJ15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BK15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BL15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BM15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BN15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BO15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BP15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BQ15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BR15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BS15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BT15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BU15" s="44" t="s">
+        <v>546</v>
+      </c>
+      <c r="BV15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BW15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BX15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BY15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="BZ15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CA15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CB15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CC15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CD15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CE15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CF15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CG15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CH15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CI15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="CJ15" s="44"/>
+      <c r="CK15" s="44"/>
+      <c r="CL15" s="44"/>
+      <c r="CM15" s="44"/>
+      <c r="CN15" s="44"/>
+      <c r="CO15" s="44"/>
+      <c r="CP15" s="44"/>
+      <c r="CQ15" s="44"/>
+      <c r="CR15" s="44"/>
+      <c r="CS15" s="44"/>
+      <c r="CT15" s="44"/>
+      <c r="CU15" s="44"/>
+      <c r="CV15" s="44"/>
+      <c r="CW15" s="44"/>
+      <c r="CX15" s="44"/>
+      <c r="CY15" s="44"/>
+      <c r="CZ15" s="44"/>
+      <c r="DA15" s="44"/>
+      <c r="DB15" s="44"/>
+      <c r="DC15" s="44"/>
+      <c r="DD15" s="44"/>
+      <c r="DE15" s="44"/>
+      <c r="DF15" s="44"/>
+      <c r="DG15" s="44"/>
+      <c r="DH15" s="44"/>
+      <c r="DI15" s="44"/>
+      <c r="DJ15" s="44"/>
+      <c r="DK15" s="44"/>
+      <c r="DL15" s="44"/>
+      <c r="DM15" s="44"/>
+      <c r="DN15" s="44"/>
+      <c r="DO15" s="44"/>
+      <c r="DP15" s="44"/>
+      <c r="DQ15" s="44"/>
+      <c r="DR15" s="44"/>
+      <c r="DS15" s="44"/>
+      <c r="DT15" s="44"/>
+      <c r="DU15" s="44"/>
+      <c r="DV15" s="44"/>
+      <c r="DW15" s="44"/>
+      <c r="DX15" s="44"/>
+      <c r="DY15" s="44"/>
+      <c r="DZ15" s="44"/>
+      <c r="EA15" s="44"/>
+      <c r="EB15" s="44"/>
+      <c r="EC15" s="44"/>
+      <c r="ED15" s="44"/>
+      <c r="EE15" s="44"/>
+      <c r="EF15" s="44"/>
+      <c r="EG15" s="44"/>
+      <c r="EH15" s="44"/>
+      <c r="EI15" s="44"/>
+      <c r="EJ15" s="44"/>
+      <c r="EK15" s="44"/>
+      <c r="EL15" s="44"/>
+      <c r="EM15" s="44"/>
+      <c r="EN15" s="44"/>
+      <c r="EO15" s="44"/>
+      <c r="EP15" s="44"/>
+      <c r="EQ15" s="44"/>
+      <c r="ER15" s="44"/>
+      <c r="ES15" s="44"/>
+      <c r="ET15" s="44"/>
+      <c r="EU15" s="44"/>
+      <c r="EV15" s="44"/>
+      <c r="EW15" s="44"/>
+      <c r="EX15" s="44"/>
+      <c r="EY15" s="44"/>
+      <c r="EZ15" s="44"/>
+      <c r="FA15" s="44"/>
+      <c r="FB15" s="44"/>
+      <c r="FC15" s="44"/>
+      <c r="FD15" s="44"/>
+      <c r="FE15" s="44"/>
+      <c r="FF15" s="44"/>
+      <c r="FG15" s="44"/>
+      <c r="FH15" s="44"/>
+      <c r="FI15" s="44"/>
+      <c r="FJ15" s="44"/>
+      <c r="FK15" s="44"/>
+      <c r="FL15" s="44"/>
+      <c r="FM15" s="44"/>
+      <c r="FN15" s="44"/>
+      <c r="FO15" s="44"/>
+      <c r="FP15" s="44"/>
+      <c r="FQ15" s="44"/>
+      <c r="FR15" s="44"/>
+      <c r="FS15" s="44"/>
+      <c r="FT15" s="44"/>
+      <c r="FU15" s="44"/>
+      <c r="FV15" s="44"/>
+      <c r="FW15" s="44"/>
+      <c r="FX15" s="44"/>
+      <c r="FY15" s="44"/>
+      <c r="FZ15" s="44"/>
+      <c r="GA15" s="44"/>
+      <c r="GB15" s="44"/>
+      <c r="GC15" s="44"/>
+      <c r="GD15" s="44"/>
+      <c r="GE15" s="44"/>
+      <c r="GF15" s="44"/>
+      <c r="GG15" s="44"/>
+      <c r="GH15" s="44"/>
+      <c r="GI15" s="44"/>
+      <c r="GJ15" s="44"/>
+      <c r="GK15" s="44"/>
+    </row>
+    <row r="16" spans="1:194" customFormat="1" ht="25.8" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="B16" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="H16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="J16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="K16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="L16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="N16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="O16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="P16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="Q16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="R16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="S16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="T16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="U16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="V16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="W16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="X16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="Y16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="Z16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AA16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AB16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AC16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AD16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AE16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AF16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AG16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AH16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AI16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AJ16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AK16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AL16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AM16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AN16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AO16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AP16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AQ16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AR16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AS16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AT16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AU16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AV16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AW16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AX16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AY16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="AZ16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BA16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BC16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BD16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BE16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BF16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BG16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BH16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BI16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BJ16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BK16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BL16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BM16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BN16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BO16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BP16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BQ16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BR16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BS16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BT16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BU16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BV16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BW16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BX16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BY16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="BZ16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CA16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CB16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CC16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CD16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CE16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CF16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CG16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CH16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CI16" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="CJ16" s="44"/>
+      <c r="CK16" s="44"/>
+      <c r="CL16" s="44"/>
+      <c r="CM16" s="44"/>
+      <c r="CN16" s="44"/>
+      <c r="CO16" s="44"/>
+      <c r="CP16" s="44"/>
+      <c r="CQ16" s="44"/>
+      <c r="CR16" s="44"/>
+      <c r="CS16" s="44"/>
+      <c r="CT16" s="44"/>
+      <c r="CU16" s="44"/>
+      <c r="CV16" s="44"/>
+      <c r="CW16" s="44"/>
+      <c r="CX16" s="44"/>
+      <c r="CY16" s="44"/>
+      <c r="CZ16" s="44"/>
+      <c r="DA16" s="44"/>
+      <c r="DB16" s="44"/>
+      <c r="DC16" s="44"/>
+      <c r="DD16" s="44"/>
+      <c r="DE16" s="44"/>
+      <c r="DF16" s="44"/>
+      <c r="DG16" s="44"/>
+      <c r="DH16" s="44"/>
+      <c r="DI16" s="44"/>
+      <c r="DJ16" s="44"/>
+      <c r="DK16" s="44"/>
+      <c r="DL16" s="44"/>
+      <c r="DM16" s="44"/>
+      <c r="DN16" s="44"/>
+      <c r="DO16" s="44"/>
+      <c r="DP16" s="44"/>
+      <c r="DQ16" s="44"/>
+      <c r="DR16" s="44"/>
+      <c r="DS16" s="44"/>
+      <c r="DT16" s="44"/>
+      <c r="DU16" s="44"/>
+      <c r="DV16" s="44"/>
+      <c r="DW16" s="44"/>
+      <c r="DX16" s="44"/>
+      <c r="DY16" s="44"/>
+      <c r="DZ16" s="44"/>
+      <c r="EA16" s="44"/>
+      <c r="EB16" s="44"/>
+      <c r="EC16" s="44"/>
+      <c r="ED16" s="44"/>
+      <c r="EE16" s="44"/>
+      <c r="EF16" s="44"/>
+      <c r="EG16" s="44"/>
+      <c r="EH16" s="44"/>
+      <c r="EI16" s="44"/>
+      <c r="EJ16" s="44"/>
+      <c r="EK16" s="44"/>
+      <c r="EL16" s="44"/>
+      <c r="EM16" s="44"/>
+      <c r="EN16" s="44"/>
+      <c r="EO16" s="44"/>
+      <c r="EP16" s="44"/>
+      <c r="EQ16" s="44"/>
+      <c r="ER16" s="44"/>
+      <c r="ES16" s="44"/>
+      <c r="ET16" s="44"/>
+      <c r="EU16" s="44"/>
+      <c r="EV16" s="44"/>
+      <c r="EW16" s="44"/>
+      <c r="EX16" s="44"/>
+      <c r="EY16" s="44"/>
+      <c r="EZ16" s="44"/>
+      <c r="FA16" s="44"/>
+      <c r="FB16" s="44"/>
+      <c r="FC16" s="44"/>
+      <c r="FD16" s="44"/>
+      <c r="FE16" s="44"/>
+      <c r="FF16" s="44"/>
+      <c r="FG16" s="44"/>
+      <c r="FH16" s="44"/>
+      <c r="FI16" s="44"/>
+      <c r="FJ16" s="44"/>
+      <c r="FK16" s="44"/>
+      <c r="FL16" s="44"/>
+      <c r="FM16" s="44"/>
+      <c r="FN16" s="44"/>
+      <c r="FO16" s="44"/>
+      <c r="FP16" s="44"/>
+      <c r="FQ16" s="44"/>
+      <c r="FR16" s="44"/>
+      <c r="FS16" s="44"/>
+      <c r="FT16" s="44"/>
+      <c r="FU16" s="44"/>
+      <c r="FV16" s="44"/>
+      <c r="FW16" s="44"/>
+      <c r="FX16" s="44"/>
+      <c r="FY16" s="44"/>
+      <c r="FZ16" s="44"/>
+      <c r="GA16" s="44"/>
+      <c r="GB16" s="44"/>
+      <c r="GC16" s="44"/>
+      <c r="GD16" s="44"/>
+      <c r="GE16" s="44"/>
+      <c r="GF16" s="44"/>
+      <c r="GG16" s="44"/>
+      <c r="GH16" s="44"/>
+      <c r="GI16" s="44"/>
+      <c r="GJ16" s="44"/>
+      <c r="GK16" s="44"/>
+    </row>
+    <row r="17" spans="1:193" s="52" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="52" t="s">
+        <v>562</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="53">
+        <v>28000</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>563</v>
+      </c>
+      <c r="E17" s="57">
+        <v>0</v>
+      </c>
+      <c r="F17" s="57">
+        <v>0</v>
+      </c>
+      <c r="G17" s="57">
+        <v>0</v>
+      </c>
+      <c r="H17" s="57">
+        <v>0</v>
+      </c>
+      <c r="I17" s="57">
+        <v>0</v>
+      </c>
+      <c r="J17" s="57">
+        <v>0</v>
+      </c>
+      <c r="K17" s="57">
+        <v>0</v>
+      </c>
+      <c r="L17" s="57">
+        <v>0</v>
+      </c>
+      <c r="M17" s="57">
+        <v>0</v>
+      </c>
+      <c r="N17" s="58">
+        <v>17280</v>
+      </c>
+      <c r="O17" s="58">
+        <v>19080</v>
+      </c>
+      <c r="P17" s="58">
+        <v>22080</v>
+      </c>
+      <c r="Q17" s="58">
+        <v>24380</v>
+      </c>
+      <c r="R17" s="58">
+        <v>27720</v>
+      </c>
+      <c r="S17" s="58">
+        <v>30220</v>
+      </c>
+      <c r="T17" s="58">
+        <v>33520</v>
+      </c>
+      <c r="U17" s="58">
+        <v>18180</v>
+      </c>
+      <c r="V17" s="58">
+        <v>19980</v>
+      </c>
+      <c r="W17" s="58">
+        <v>23680</v>
+      </c>
+      <c r="X17" s="58">
+        <v>24780</v>
+      </c>
+      <c r="Y17" s="58">
+        <v>27920</v>
+      </c>
+      <c r="Z17" s="58">
+        <v>30220</v>
+      </c>
+      <c r="AA17" s="58">
+        <v>32720</v>
+      </c>
+      <c r="AB17" s="58">
+        <v>37520</v>
+      </c>
+      <c r="AC17" s="58">
+        <v>41520</v>
+      </c>
+      <c r="AD17" s="58"/>
+      <c r="AE17" s="58"/>
+      <c r="AF17" s="58"/>
+      <c r="AG17" s="58"/>
+      <c r="AH17" s="58"/>
+      <c r="AI17" s="58"/>
+      <c r="AJ17" s="58"/>
+      <c r="AK17" s="58">
+        <v>14080</v>
+      </c>
+      <c r="AL17" s="58">
+        <v>16180</v>
+      </c>
+      <c r="AM17" s="58">
+        <v>17480</v>
+      </c>
+      <c r="AN17" s="58">
+        <v>19980</v>
+      </c>
+      <c r="AO17" s="58">
+        <v>23820</v>
+      </c>
+      <c r="AP17" s="58">
+        <v>27220</v>
+      </c>
+      <c r="AQ17" s="58">
+        <v>30220</v>
+      </c>
+      <c r="AR17" s="58"/>
+      <c r="AS17" s="58"/>
+      <c r="AT17" s="58"/>
+      <c r="AU17" s="58"/>
+      <c r="AV17" s="58"/>
+      <c r="AW17" s="58"/>
+      <c r="AX17" s="58"/>
+      <c r="AY17" s="58">
+        <v>12980</v>
+      </c>
+      <c r="AZ17" s="58">
+        <v>14080</v>
+      </c>
+      <c r="BA17" s="58">
+        <v>15380</v>
+      </c>
+      <c r="BB17" s="58">
+        <v>18280</v>
+      </c>
+      <c r="BC17" s="58">
+        <v>21520</v>
+      </c>
+      <c r="BD17" s="58">
+        <v>24320</v>
+      </c>
+      <c r="BE17" s="58">
+        <v>27320</v>
+      </c>
+      <c r="BF17" s="58">
+        <v>16680</v>
+      </c>
+      <c r="BG17" s="58">
+        <v>17980</v>
+      </c>
+      <c r="BH17" s="58">
+        <v>20280</v>
+      </c>
+      <c r="BI17" s="58">
+        <v>22080</v>
+      </c>
+      <c r="BJ17" s="58">
+        <v>25020</v>
+      </c>
+      <c r="BK17" s="58">
+        <v>25620</v>
+      </c>
+      <c r="BL17" s="58">
+        <v>27720</v>
+      </c>
+      <c r="BM17" s="58">
+        <v>17280</v>
+      </c>
+      <c r="BN17" s="58">
+        <v>19080</v>
+      </c>
+      <c r="BO17" s="58">
+        <v>22080</v>
+      </c>
+      <c r="BP17" s="58">
+        <v>24380</v>
+      </c>
+      <c r="BQ17" s="58">
+        <v>27720</v>
+      </c>
+      <c r="BR17" s="58">
+        <v>30220</v>
+      </c>
+      <c r="BS17" s="58">
+        <v>33520</v>
+      </c>
+      <c r="BT17" s="58">
+        <v>34100</v>
+      </c>
+      <c r="BU17" s="58">
+        <v>38100</v>
+      </c>
+      <c r="BV17" s="58">
+        <v>16680</v>
+      </c>
+      <c r="BW17" s="58">
+        <v>17980</v>
+      </c>
+      <c r="BX17" s="58">
+        <v>20280</v>
+      </c>
+      <c r="BY17" s="58">
+        <v>22080</v>
+      </c>
+      <c r="BZ17" s="58">
+        <v>25020</v>
+      </c>
+      <c r="CA17" s="58">
+        <v>25620</v>
+      </c>
+      <c r="CB17" s="58">
+        <v>27720</v>
+      </c>
+      <c r="CC17" s="58">
+        <v>12980</v>
+      </c>
+      <c r="CD17" s="58">
+        <v>14080</v>
+      </c>
+      <c r="CE17" s="58">
+        <v>15380</v>
+      </c>
+      <c r="CF17" s="58">
+        <v>18280</v>
+      </c>
+      <c r="CG17" s="58">
+        <v>21520</v>
+      </c>
+      <c r="CH17" s="58">
+        <v>24320</v>
+      </c>
+      <c r="CI17" s="58">
+        <v>27320</v>
+      </c>
+      <c r="CJ17" s="58">
+        <v>26200</v>
+      </c>
+      <c r="CK17" s="58">
+        <v>27200</v>
+      </c>
+      <c r="CL17" s="58">
+        <v>28700</v>
+      </c>
+      <c r="CM17" s="58">
+        <v>30600</v>
+      </c>
+      <c r="CN17" s="58">
+        <v>32800</v>
+      </c>
+      <c r="CO17" s="58">
+        <v>35200</v>
+      </c>
+      <c r="CP17" s="58">
+        <v>29000</v>
+      </c>
+      <c r="CQ17" s="58">
+        <v>29900</v>
+      </c>
+      <c r="CR17" s="58">
+        <v>31500</v>
+      </c>
+      <c r="CS17" s="58">
+        <v>33400</v>
+      </c>
+      <c r="CT17" s="58">
+        <v>35700</v>
+      </c>
+      <c r="CU17" s="58">
+        <v>38100</v>
+      </c>
+      <c r="CV17" s="58">
+        <v>34800</v>
+      </c>
+      <c r="CW17" s="58">
+        <v>36100</v>
+      </c>
+      <c r="CX17" s="58">
+        <v>37200</v>
+      </c>
+      <c r="CY17" s="58">
+        <v>39000</v>
+      </c>
+      <c r="CZ17" s="58">
+        <v>40100</v>
+      </c>
+      <c r="DA17" s="58">
+        <v>43700</v>
+      </c>
+      <c r="DB17" s="58">
+        <v>48300</v>
+      </c>
+      <c r="DC17" s="58">
+        <v>51200</v>
+      </c>
+      <c r="DD17" s="58">
+        <v>53800</v>
+      </c>
+      <c r="DE17" s="58">
+        <v>62700</v>
+      </c>
+      <c r="DF17" s="58">
+        <v>36000</v>
+      </c>
+      <c r="DG17" s="58">
+        <v>37100</v>
+      </c>
+      <c r="DH17" s="58">
+        <v>38300</v>
+      </c>
+      <c r="DI17" s="58">
+        <v>40100</v>
+      </c>
+      <c r="DJ17" s="58">
+        <v>41100</v>
+      </c>
+      <c r="DK17" s="58">
+        <v>44700</v>
+      </c>
+      <c r="DL17" s="58">
+        <v>49300</v>
+      </c>
+      <c r="DM17" s="58">
+        <v>52300</v>
+      </c>
+      <c r="DN17" s="58">
+        <v>54800</v>
+      </c>
+      <c r="DO17" s="58">
+        <v>63800</v>
+      </c>
+      <c r="DP17" s="58">
+        <v>92800</v>
+      </c>
+      <c r="DQ17" s="58">
+        <v>98000</v>
+      </c>
+      <c r="DR17" s="58">
+        <v>110000</v>
+      </c>
+      <c r="DS17" s="58">
+        <v>116000</v>
+      </c>
+      <c r="DT17" s="58">
+        <v>108100</v>
+      </c>
+      <c r="DU17" s="58">
+        <v>129800</v>
+      </c>
+      <c r="DV17" s="58">
+        <v>140900</v>
+      </c>
+      <c r="DW17" s="58">
+        <v>57100</v>
+      </c>
+      <c r="DX17" s="58">
+        <v>79500</v>
+      </c>
+      <c r="DY17" s="58">
+        <v>113200</v>
+      </c>
+      <c r="DZ17" s="58">
+        <v>120300</v>
+      </c>
+      <c r="EA17" s="58">
+        <v>105000</v>
+      </c>
+      <c r="EB17" s="58">
+        <v>40000</v>
+      </c>
+      <c r="EC17" s="58">
+        <v>41400</v>
+      </c>
+      <c r="ED17" s="58">
+        <v>43100</v>
+      </c>
+      <c r="EE17" s="58">
+        <v>44300</v>
+      </c>
+      <c r="EF17" s="58">
+        <v>45400</v>
+      </c>
+      <c r="EG17" s="58">
+        <v>50000</v>
+      </c>
+      <c r="EH17" s="58">
+        <v>52900</v>
+      </c>
+      <c r="EI17" s="58">
+        <v>55500</v>
+      </c>
+      <c r="EJ17" s="58">
+        <v>64400</v>
+      </c>
+      <c r="EK17" s="58">
+        <v>43200</v>
+      </c>
+      <c r="EL17" s="58">
+        <v>45300</v>
+      </c>
+      <c r="EM17" s="58">
+        <v>47700</v>
+      </c>
+      <c r="EN17" s="58">
+        <v>48400</v>
+      </c>
+      <c r="EO17" s="58">
+        <v>49100</v>
+      </c>
+      <c r="EP17" s="58">
+        <v>53100</v>
+      </c>
+      <c r="EQ17" s="58">
+        <v>56300</v>
+      </c>
+      <c r="ER17" s="58">
+        <v>59500</v>
+      </c>
+      <c r="ES17" s="58">
+        <v>69500</v>
+      </c>
+      <c r="ET17" s="58">
+        <v>34300</v>
+      </c>
+      <c r="EU17" s="58">
+        <v>35400</v>
+      </c>
+      <c r="EV17" s="58">
+        <v>36500</v>
+      </c>
+      <c r="EW17" s="58">
+        <v>36800</v>
+      </c>
+      <c r="EX17" s="58">
+        <v>37000</v>
+      </c>
+      <c r="EY17" s="58">
+        <v>42100</v>
+      </c>
+      <c r="EZ17" s="58">
+        <v>45300</v>
+      </c>
+      <c r="FA17" s="58">
+        <v>51300</v>
+      </c>
+      <c r="FB17" s="58">
+        <v>59800</v>
+      </c>
+      <c r="FC17" s="58">
+        <v>185000</v>
+      </c>
+      <c r="FD17" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="FE17" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="FF17" s="58">
+        <v>34500</v>
+      </c>
+      <c r="FG17" s="58">
+        <v>38500</v>
+      </c>
+      <c r="FH17" s="58">
+        <v>39900</v>
+      </c>
+      <c r="FI17" s="58">
+        <v>41100</v>
+      </c>
+      <c r="FJ17" s="58">
+        <v>42300</v>
+      </c>
+      <c r="FK17" s="58">
+        <v>42000</v>
+      </c>
+      <c r="FL17" s="58">
+        <v>44200</v>
+      </c>
+      <c r="FM17" s="58">
+        <v>45800</v>
+      </c>
+      <c r="FN17" s="58">
+        <v>46900</v>
+      </c>
+      <c r="FO17" s="58">
+        <v>49800</v>
+      </c>
+      <c r="FP17" s="58">
+        <v>54800</v>
+      </c>
+      <c r="FQ17" s="58">
+        <v>61300</v>
+      </c>
+      <c r="FR17" s="58">
+        <v>66800</v>
+      </c>
+      <c r="FS17" s="58"/>
+      <c r="FT17" s="58"/>
+      <c r="FU17" s="58"/>
+      <c r="FV17" s="58"/>
+      <c r="FW17" s="58"/>
+      <c r="FX17" s="58"/>
+      <c r="FY17" s="58"/>
+      <c r="FZ17" s="58"/>
+      <c r="GA17" s="58"/>
+      <c r="GB17" s="58"/>
+      <c r="GC17" s="58"/>
+      <c r="GD17" s="58"/>
+      <c r="GE17" s="58"/>
+      <c r="GF17" s="58"/>
+      <c r="GG17" s="58"/>
+      <c r="GH17" s="58"/>
+      <c r="GI17" s="58"/>
+      <c r="GJ17" s="58"/>
+      <c r="GK17" s="58"/>
+    </row>
+    <row r="18" spans="1:193" s="40" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A18" s="59" t="s">
+        <v>567</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="CJ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CK18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CL18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CM18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CN18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CO18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CP18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CQ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CR18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CS18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CT18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CU18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CV18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CW18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CX18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CY18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="CZ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DA18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DB18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DC18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DD18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DE18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DF18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DG18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DH18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DI18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DJ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DK18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DL18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DM18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DN18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DO18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DP18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DQ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DR18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DS18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DT18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DU18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DV18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DW18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DX18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DY18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="DZ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EA18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EB18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EC18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="ED18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EE18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EF18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EG18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EH18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EI18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EJ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EK18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EL18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EM18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EN18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EO18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EP18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EQ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="ER18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="ES18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="ET18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EU18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EV18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EW18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EX18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EY18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="EZ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FA18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FB18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FC18" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="FF18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FG18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FH18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FI18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FJ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FK18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FL18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FM18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FN18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FO18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FP18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FQ18" s="40" t="s">
+        <v>571</v>
+      </c>
+      <c r="FR18" s="40" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="19" spans="1:193" s="40" customFormat="1" ht="12" x14ac:dyDescent="0.3">
+      <c r="A19" s="59" t="s">
+        <v>568</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="CJ19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CK19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CL19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CM19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CN19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CO19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CP19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CQ19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CR19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CS19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CT19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CU19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CV19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CW19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CX19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CY19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="CZ19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DA19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DB19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DC19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DD19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DE19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DF19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DG19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DH19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DI19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DJ19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DK19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DL19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DM19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DN19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DO19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DP19" s="40" t="s">
+        <v>573</v>
+      </c>
+      <c r="DQ19" s="40" t="s">
+        <v>573</v>
+      </c>
+      <c r="DR19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="DS19" s="40" t="s">
+        <v>572</v>
+      </c>
+      <c r="EB19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EC19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="ED19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EE19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EF19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EG19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EH19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EI19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EJ19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EK19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EL19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EM19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EN19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EO19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EP19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="EQ19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="ER19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="ES19" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="ET19" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="EU19" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="EV19" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="EW19" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="EX19" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="EY19" s="40" t="s">
+        <v>575</v>
+      </c>
+      <c r="EZ19" s="40" t="s">
+        <v>576</v>
+      </c>
+      <c r="FA19" s="40" t="s">
+        <v>576</v>
+      </c>
+      <c r="FB19" s="40" t="s">
+        <v>576</v>
+      </c>
+      <c r="FC19" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="FF19" s="40" t="s">
+        <v>577</v>
+      </c>
+      <c r="FG19" s="40" t="s">
+        <v>577</v>
+      </c>
+      <c r="FH19" s="40" t="s">
+        <v>577</v>
+      </c>
+      <c r="FI19" s="40" t="s">
+        <v>577</v>
+      </c>
+      <c r="FJ19" s="40" t="s">
+        <v>577</v>
+      </c>
+      <c r="FK19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FL19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FM19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FN19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FO19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FP19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FQ19" s="40" t="s">
+        <v>578</v>
+      </c>
+      <c r="FR19" s="40" t="s">
+        <v>578</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9198,18 +12020,230 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F00506A-09F5-4009-80F2-281B4A4C3425}">
+  <dimension ref="A2:F19"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="62" t="s">
+        <v>580</v>
+      </c>
+      <c r="B3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C3">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C4">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>591</v>
+      </c>
+      <c r="B5" t="s">
+        <v>590</v>
+      </c>
+      <c r="C5">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>584</v>
+      </c>
+      <c r="B6" t="s">
+        <v>586</v>
+      </c>
+      <c r="C6">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>585</v>
+      </c>
+      <c r="B7" t="s">
+        <v>587</v>
+      </c>
+      <c r="C7">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="62" t="s">
+        <v>588</v>
+      </c>
+      <c r="B8" t="s">
+        <v>592</v>
+      </c>
+      <c r="C8">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>589</v>
+      </c>
+      <c r="B9" t="s">
+        <v>593</v>
+      </c>
+      <c r="C9">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="62" t="s">
+        <v>594</v>
+      </c>
+      <c r="B10" t="s">
+        <v>595</v>
+      </c>
+      <c r="C10">
+        <v>108200</v>
+      </c>
+      <c r="F10" s="63"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>596</v>
+      </c>
+      <c r="B11" t="s">
+        <v>597</v>
+      </c>
+      <c r="C11">
+        <v>28600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>598</v>
+      </c>
+      <c r="B12" t="s">
+        <v>599</v>
+      </c>
+      <c r="C12">
+        <v>19400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>601</v>
+      </c>
+      <c r="B13" t="s">
+        <v>602</v>
+      </c>
+      <c r="C13">
+        <v>19400</v>
+      </c>
+      <c r="D13" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>600</v>
+      </c>
+      <c r="B14" t="s">
+        <v>607</v>
+      </c>
+      <c r="C14">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="62" t="s">
+        <v>604</v>
+      </c>
+      <c r="B15" t="s">
+        <v>605</v>
+      </c>
+      <c r="C15">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="62" t="s">
+        <v>608</v>
+      </c>
+      <c r="B16" t="s">
+        <v>606</v>
+      </c>
+      <c r="C16">
+        <v>83600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>609</v>
+      </c>
+      <c r="B17" t="s">
+        <v>610</v>
+      </c>
+      <c r="C17">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="62" t="s">
+        <v>611</v>
+      </c>
+      <c r="B18" t="s">
+        <v>612</v>
+      </c>
+      <c r="C18">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="62" t="s">
+        <v>613</v>
+      </c>
+      <c r="B19" t="s">
+        <v>614</v>
+      </c>
+      <c r="C19">
+        <v>34700</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14518F8B-544C-42CB-BD27-24B9976359F4}">
-  <dimension ref="A1:FG13"/>
+  <dimension ref="A1:FH15"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
     <col min="2" max="2" width="13.44140625" customWidth="1"/>
     <col min="3" max="3" width="16.44140625" style="7" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="34.44140625" hidden="1" customWidth="1"/>
-    <col min="5" max="130" width="14.6640625" customWidth="1"/>
+    <col min="5" max="131" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -9223,7 +12257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:163" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:164" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -9411,7 +12445,7 @@
         <v>34</v>
       </c>
       <c r="BK2" s="5" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="BL2" s="5" t="s">
         <v>133</v>
@@ -9614,7 +12648,9 @@
       <c r="DZ2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="EA2" s="5"/>
+      <c r="EA2" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="EB2" s="5"/>
       <c r="EC2" s="5"/>
       <c r="ED2" s="5"/>
@@ -9647,8 +12683,9 @@
       <c r="FE2" s="5"/>
       <c r="FF2" s="5"/>
       <c r="FG2" s="5"/>
+      <c r="FH2" s="5"/>
     </row>
-    <row r="3" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -9836,10 +12873,10 @@
         <v>476</v>
       </c>
       <c r="BK3" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="BL3" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="BL3" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="BM3" s="5" t="s">
         <v>130</v>
@@ -9854,13 +12891,13 @@
         <v>130</v>
       </c>
       <c r="BQ3" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BR3" s="5" t="s">
         <v>131</v>
       </c>
       <c r="BS3" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BT3" s="5" t="s">
         <v>132</v>
@@ -9869,7 +12906,7 @@
         <v>132</v>
       </c>
       <c r="BV3" s="5" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="BW3" s="5" t="s">
         <v>146</v>
@@ -9878,7 +12915,7 @@
         <v>146</v>
       </c>
       <c r="BY3" s="5" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="BZ3" s="5" t="s">
         <v>190</v>
@@ -9959,7 +12996,7 @@
         <v>190</v>
       </c>
       <c r="CZ3" s="5" t="s">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="DA3" s="5" t="s">
         <v>42</v>
@@ -10039,7 +13076,9 @@
       <c r="DZ3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="EA3" s="5"/>
+      <c r="EA3" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="EB3" s="5"/>
       <c r="EC3" s="5"/>
       <c r="ED3" s="5"/>
@@ -10072,8 +13111,9 @@
       <c r="FE3" s="5"/>
       <c r="FF3" s="5"/>
       <c r="FG3" s="5"/>
+      <c r="FH3" s="5"/>
     </row>
-    <row r="4" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>52</v>
       </c>
@@ -10261,210 +13301,212 @@
         <v>109</v>
       </c>
       <c r="BK4" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="BL4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="BL4" s="5" t="s">
+      <c r="BM4" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="BM4" s="5" t="s">
+      <c r="BN4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="BN4" s="5" t="s">
+      <c r="BO4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="BO4" s="5" t="s">
+      <c r="BP4" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="BP4" s="5" t="s">
+      <c r="BQ4" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="BQ4" s="5" t="s">
+      <c r="BR4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="BR4" s="5" t="s">
+      <c r="BS4" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="BS4" s="5" t="s">
+      <c r="BT4" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="BT4" s="5" t="s">
+      <c r="BU4" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="BU4" s="5" t="s">
+      <c r="BV4" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="BV4" s="5" t="s">
+      <c r="BW4" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="BW4" s="5" t="s">
+      <c r="BX4" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="BX4" s="5" t="s">
+      <c r="BY4" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="BY4" s="5" t="s">
+      <c r="BZ4" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="BZ4" s="5" t="s">
+      <c r="CA4" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="CA4" s="5" t="s">
+      <c r="CB4" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="CB4" s="5" t="s">
+      <c r="CC4" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="CC4" s="5" t="s">
+      <c r="CD4" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="CD4" s="5" t="s">
+      <c r="CE4" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="CE4" s="5" t="s">
+      <c r="CF4" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="CF4" s="5" t="s">
+      <c r="CG4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="CG4" s="5" t="s">
+      <c r="CH4" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="CH4" s="5" t="s">
+      <c r="CI4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="CI4" s="5" t="s">
+      <c r="CJ4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="CJ4" s="5" t="s">
+      <c r="CK4" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="CK4" s="5" t="s">
+      <c r="CL4" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="CL4" s="5" t="s">
+      <c r="CM4" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="CM4" s="5" t="s">
+      <c r="CN4" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="CN4" s="5" t="s">
+      <c r="CO4" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="CO4" s="5" t="s">
+      <c r="CP4" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="CP4" s="5" t="s">
+      <c r="CQ4" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="CQ4" s="5" t="s">
+      <c r="CR4" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="CR4" s="5" t="s">
+      <c r="CS4" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="CS4" s="5" t="s">
+      <c r="CT4" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="CT4" s="5" t="s">
+      <c r="CU4" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="CU4" s="5" t="s">
+      <c r="CV4" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="CV4" s="5" t="s">
+      <c r="CW4" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="CW4" s="5" t="s">
+      <c r="CX4" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="CX4" s="5" t="s">
+      <c r="CY4" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="CY4" s="5" t="s">
+      <c r="CZ4" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="CZ4" s="5" t="s">
+      <c r="DA4" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="DA4" s="5" t="s">
+      <c r="DB4" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="DB4" s="5" t="s">
+      <c r="DC4" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="DC4" s="5" t="s">
+      <c r="DD4" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="DD4" s="5" t="s">
+      <c r="DE4" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="DE4" s="5" t="s">
+      <c r="DF4" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="DF4" s="5" t="s">
+      <c r="DG4" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="DG4" s="5" t="s">
+      <c r="DH4" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="DH4" s="5" t="s">
+      <c r="DI4" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="DI4" s="5" t="s">
+      <c r="DJ4" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="DJ4" s="5" t="s">
+      <c r="DK4" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="DK4" s="5" t="s">
+      <c r="DL4" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="DL4" s="5" t="s">
+      <c r="DM4" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="DM4" s="5" t="s">
+      <c r="DN4" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="DN4" s="5" t="s">
+      <c r="DO4" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="DO4" s="5" t="s">
+      <c r="DP4" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="DP4" s="5" t="s">
+      <c r="DQ4" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="DQ4" s="5" t="s">
+      <c r="DR4" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="DR4" s="5" t="s">
+      <c r="DS4" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="DS4" s="5" t="s">
+      <c r="DT4" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="DT4" s="5" t="s">
+      <c r="DU4" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="DU4" s="5" t="s">
+      <c r="DV4" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="DV4" s="5" t="s">
+      <c r="DW4" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="DW4" s="5" t="s">
+      <c r="DX4" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="DX4" s="5" t="s">
+      <c r="DY4" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="DY4" s="5" t="s">
+      <c r="DZ4" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="DZ4" s="5" t="s">
+      <c r="EA4" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="EA4" s="5"/>
       <c r="EB4" s="5"/>
       <c r="EC4" s="5"/>
       <c r="ED4" s="5"/>
@@ -10497,8 +13539,9 @@
       <c r="FE4" s="5"/>
       <c r="FF4" s="5"/>
       <c r="FG4" s="5"/>
+      <c r="FH4" s="5"/>
     </row>
-    <row r="5" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
@@ -10686,210 +13729,212 @@
         <v>5</v>
       </c>
       <c r="BK5" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="BL5" s="5">
         <v>11.2</v>
       </c>
-      <c r="BL5" s="5">
+      <c r="BM5" s="5">
         <v>12.5</v>
       </c>
-      <c r="BM5" s="5">
+      <c r="BN5" s="5">
         <v>14</v>
       </c>
-      <c r="BN5" s="5">
+      <c r="BO5" s="5">
         <v>16</v>
       </c>
-      <c r="BO5" s="5">
+      <c r="BP5" s="5">
         <v>28</v>
       </c>
-      <c r="BP5" s="5">
+      <c r="BQ5" s="5">
         <v>33.5</v>
       </c>
-      <c r="BQ5" s="5">
+      <c r="BR5" s="5">
         <v>22.4</v>
       </c>
-      <c r="BR5" s="5">
+      <c r="BS5" s="5">
         <v>25</v>
       </c>
-      <c r="BS5" s="5">
+      <c r="BT5" s="5">
         <v>15.5</v>
       </c>
-      <c r="BT5" s="5">
+      <c r="BU5" s="5">
         <v>20</v>
       </c>
-      <c r="BU5" s="5">
+      <c r="BV5" s="5">
         <v>24</v>
       </c>
-      <c r="BV5" s="5">
+      <c r="BW5" s="5">
         <v>11.2</v>
       </c>
-      <c r="BW5" s="5">
+      <c r="BX5" s="5">
         <v>12.5</v>
       </c>
-      <c r="BX5" s="5">
+      <c r="BY5" s="5">
         <v>14</v>
       </c>
-      <c r="BY5" s="5">
+      <c r="BZ5" s="5">
         <v>22.4</v>
       </c>
-      <c r="BZ5" s="5">
+      <c r="CA5" s="5">
         <v>28</v>
       </c>
-      <c r="CA5" s="5">
+      <c r="CB5" s="5">
         <v>33.5</v>
       </c>
-      <c r="CB5" s="5">
+      <c r="CC5" s="5">
         <v>40</v>
       </c>
-      <c r="CC5" s="5">
+      <c r="CD5" s="5">
         <v>45</v>
       </c>
-      <c r="CD5" s="5">
+      <c r="CE5" s="5">
         <v>50</v>
       </c>
-      <c r="CE5" s="5">
+      <c r="CF5" s="5">
         <v>54</v>
       </c>
-      <c r="CF5" s="5">
+      <c r="CG5" s="5">
         <v>61.5</v>
       </c>
-      <c r="CG5" s="5">
+      <c r="CH5" s="5">
         <v>67</v>
       </c>
-      <c r="CH5" s="5">
+      <c r="CI5" s="5">
         <v>73.5</v>
       </c>
-      <c r="CI5" s="5">
+      <c r="CJ5" s="5">
         <v>78.5</v>
       </c>
-      <c r="CJ5" s="5">
+      <c r="CK5" s="5">
         <v>85</v>
       </c>
-      <c r="CK5" s="5">
+      <c r="CL5" s="5">
         <v>90</v>
       </c>
-      <c r="CL5" s="5">
+      <c r="CM5" s="5">
         <v>95</v>
       </c>
-      <c r="CM5" s="5">
+      <c r="CN5" s="5">
         <v>100</v>
       </c>
-      <c r="CN5" s="5">
+      <c r="CO5" s="5">
         <v>104</v>
       </c>
-      <c r="CO5" s="5">
+      <c r="CP5" s="5">
         <v>108</v>
       </c>
-      <c r="CP5" s="5">
+      <c r="CQ5" s="5">
         <v>117</v>
       </c>
-      <c r="CQ5" s="5">
+      <c r="CR5" s="5">
         <v>121</v>
       </c>
-      <c r="CR5" s="5">
+      <c r="CS5" s="5">
         <v>130</v>
       </c>
-      <c r="CS5" s="5">
+      <c r="CT5" s="5">
         <v>135</v>
       </c>
-      <c r="CT5" s="5">
+      <c r="CU5" s="5">
         <v>140</v>
       </c>
-      <c r="CU5" s="5">
+      <c r="CV5" s="5">
         <v>145</v>
       </c>
-      <c r="CV5" s="5">
+      <c r="CW5" s="5">
         <v>150</v>
       </c>
-      <c r="CW5" s="5">
+      <c r="CX5" s="5">
         <v>154</v>
       </c>
-      <c r="CX5" s="5">
+      <c r="CY5" s="5">
         <v>158</v>
       </c>
-      <c r="CY5" s="5">
+      <c r="CZ5" s="5">
         <v>162</v>
       </c>
-      <c r="CZ5" s="5">
+      <c r="DA5" s="5">
         <v>22.4</v>
       </c>
-      <c r="DA5" s="5">
+      <c r="DB5" s="5">
         <v>28</v>
       </c>
-      <c r="DB5" s="5">
+      <c r="DC5" s="5">
         <v>33.5</v>
       </c>
-      <c r="DC5" s="5">
+      <c r="DD5" s="5">
         <v>40</v>
       </c>
-      <c r="DD5" s="5">
+      <c r="DE5" s="5">
         <v>45</v>
       </c>
-      <c r="DE5" s="5">
+      <c r="DF5" s="5">
         <v>50</v>
       </c>
-      <c r="DF5" s="5">
+      <c r="DG5" s="5">
         <v>54</v>
       </c>
-      <c r="DG5" s="5">
+      <c r="DH5" s="5">
         <v>61.5</v>
       </c>
-      <c r="DH5" s="5">
+      <c r="DI5" s="5">
         <v>67</v>
       </c>
-      <c r="DI5" s="5">
+      <c r="DJ5" s="5">
         <v>73.5</v>
       </c>
-      <c r="DJ5" s="5">
+      <c r="DK5" s="5">
         <v>78.5</v>
       </c>
-      <c r="DK5" s="5">
+      <c r="DL5" s="5">
         <v>85</v>
       </c>
-      <c r="DL5" s="5">
+      <c r="DM5" s="5">
         <v>90</v>
       </c>
-      <c r="DM5" s="5">
+      <c r="DN5" s="5">
         <v>95</v>
       </c>
-      <c r="DN5" s="5">
+      <c r="DO5" s="5">
         <v>100</v>
       </c>
-      <c r="DO5" s="5">
+      <c r="DP5" s="5">
         <v>104</v>
       </c>
-      <c r="DP5" s="5">
+      <c r="DQ5" s="5">
         <v>108</v>
       </c>
-      <c r="DQ5" s="5">
+      <c r="DR5" s="5">
         <v>117</v>
       </c>
-      <c r="DR5" s="5">
+      <c r="DS5" s="5">
         <v>121</v>
       </c>
-      <c r="DS5" s="5">
+      <c r="DT5" s="5">
         <v>130</v>
       </c>
-      <c r="DT5" s="5">
+      <c r="DU5" s="5">
         <v>135</v>
       </c>
-      <c r="DU5" s="5">
+      <c r="DV5" s="5">
         <v>140</v>
       </c>
-      <c r="DV5" s="5">
+      <c r="DW5" s="5">
         <v>145</v>
       </c>
-      <c r="DW5" s="5">
+      <c r="DX5" s="5">
         <v>150</v>
       </c>
-      <c r="DX5" s="5">
+      <c r="DY5" s="5">
         <v>154</v>
       </c>
-      <c r="DY5" s="5">
+      <c r="DZ5" s="5">
         <v>158</v>
       </c>
-      <c r="DZ5" s="5">
+      <c r="EA5" s="5">
         <v>162</v>
       </c>
-      <c r="EA5" s="5"/>
       <c r="EB5" s="5"/>
       <c r="EC5" s="5"/>
       <c r="ED5" s="5"/>
@@ -10922,8 +13967,9 @@
       <c r="FE5" s="5"/>
       <c r="FF5" s="5"/>
       <c r="FG5" s="5"/>
+      <c r="FH5" s="5"/>
     </row>
-    <row r="6" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>45</v>
       </c>
@@ -11110,211 +14156,213 @@
       <c r="BJ6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="BK6" s="5">
+      <c r="BK6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="BL6" s="5">
         <v>100</v>
       </c>
-      <c r="BL6" s="5">
+      <c r="BM6" s="5">
         <v>112.5</v>
       </c>
-      <c r="BM6" s="5">
+      <c r="BN6" s="5">
         <v>125</v>
       </c>
-      <c r="BN6" s="5">
+      <c r="BO6" s="5">
         <v>150</v>
       </c>
-      <c r="BO6" s="5">
+      <c r="BP6" s="5">
         <v>250</v>
       </c>
-      <c r="BP6" s="5">
+      <c r="BQ6" s="5">
         <v>300</v>
       </c>
-      <c r="BQ6" s="5">
+      <c r="BR6" s="5">
         <v>200</v>
       </c>
-      <c r="BR6" s="5">
+      <c r="BS6" s="5">
         <v>223</v>
       </c>
-      <c r="BS6" s="5">
+      <c r="BT6" s="5">
         <v>140</v>
       </c>
-      <c r="BT6" s="5">
+      <c r="BU6" s="5">
         <v>180</v>
       </c>
-      <c r="BU6" s="5">
+      <c r="BV6" s="5">
         <v>215</v>
       </c>
-      <c r="BV6" s="5">
+      <c r="BW6" s="5">
         <v>100</v>
       </c>
-      <c r="BW6" s="5">
+      <c r="BX6" s="5">
         <v>112.5</v>
       </c>
-      <c r="BX6" s="5">
+      <c r="BY6" s="5">
         <v>125</v>
       </c>
-      <c r="BY6" s="5">
+      <c r="BZ6" s="5">
         <v>200</v>
       </c>
-      <c r="BZ6" s="5">
+      <c r="CA6" s="5">
         <v>250</v>
       </c>
-      <c r="CA6" s="5">
+      <c r="CB6" s="5">
         <v>300</v>
       </c>
-      <c r="CB6" s="5">
+      <c r="CC6" s="5">
         <v>350</v>
       </c>
-      <c r="CC6" s="5">
+      <c r="CD6" s="5">
         <v>400</v>
       </c>
-      <c r="CD6" s="5">
+      <c r="CE6" s="5">
         <v>450</v>
       </c>
-      <c r="CE6" s="5">
+      <c r="CF6" s="5">
         <v>500</v>
       </c>
-      <c r="CF6" s="5">
+      <c r="CG6" s="5">
         <v>550</v>
       </c>
-      <c r="CG6" s="5">
+      <c r="CH6" s="5">
         <v>600</v>
       </c>
-      <c r="CH6" s="5">
+      <c r="CI6" s="5">
         <v>650</v>
       </c>
-      <c r="CI6" s="5">
+      <c r="CJ6" s="5">
         <v>700</v>
       </c>
-      <c r="CJ6" s="5">
+      <c r="CK6" s="5">
         <v>750</v>
       </c>
-      <c r="CK6" s="5">
+      <c r="CL6" s="5">
         <v>800</v>
       </c>
-      <c r="CL6" s="5">
+      <c r="CM6" s="5">
         <v>850</v>
       </c>
-      <c r="CM6" s="5">
+      <c r="CN6" s="5">
         <v>900</v>
       </c>
-      <c r="CN6" s="5">
+      <c r="CO6" s="5">
         <v>950</v>
       </c>
-      <c r="CO6" s="5">
+      <c r="CP6" s="5">
         <v>1000</v>
       </c>
-      <c r="CP6" s="5">
+      <c r="CQ6" s="5">
         <v>1050</v>
       </c>
-      <c r="CQ6" s="5">
+      <c r="CR6" s="5">
         <v>1100</v>
       </c>
-      <c r="CR6" s="5">
+      <c r="CS6" s="5">
         <v>1150</v>
       </c>
-      <c r="CS6" s="5">
+      <c r="CT6" s="5">
         <v>1200</v>
       </c>
-      <c r="CT6" s="5">
+      <c r="CU6" s="5">
         <v>1250</v>
       </c>
-      <c r="CU6" s="5">
+      <c r="CV6" s="5">
         <v>1300</v>
       </c>
-      <c r="CV6" s="5">
+      <c r="CW6" s="5">
         <v>1350</v>
       </c>
-      <c r="CW6" s="5">
+      <c r="CX6" s="5">
         <v>1400</v>
       </c>
-      <c r="CX6" s="5">
+      <c r="CY6" s="5">
         <v>1450</v>
       </c>
-      <c r="CY6" s="5">
+      <c r="CZ6" s="5">
         <v>1500</v>
       </c>
-      <c r="CZ6" s="5">
+      <c r="DA6" s="5">
         <v>200</v>
       </c>
-      <c r="DA6" s="5">
+      <c r="DB6" s="5">
         <v>250</v>
       </c>
-      <c r="DB6" s="5">
+      <c r="DC6" s="5">
         <v>300</v>
       </c>
-      <c r="DC6" s="5">
+      <c r="DD6" s="5">
         <v>350</v>
       </c>
-      <c r="DD6" s="5">
+      <c r="DE6" s="5">
         <v>400</v>
       </c>
-      <c r="DE6" s="5">
+      <c r="DF6" s="5">
         <v>450</v>
       </c>
-      <c r="DF6" s="5">
+      <c r="DG6" s="5">
         <v>500</v>
       </c>
-      <c r="DG6" s="5">
+      <c r="DH6" s="5">
         <v>550</v>
       </c>
-      <c r="DH6" s="5">
+      <c r="DI6" s="5">
         <v>600</v>
       </c>
-      <c r="DI6" s="5">
+      <c r="DJ6" s="5">
         <v>650</v>
       </c>
-      <c r="DJ6" s="5">
+      <c r="DK6" s="5">
         <v>700</v>
       </c>
-      <c r="DK6" s="5">
+      <c r="DL6" s="5">
         <v>750</v>
       </c>
-      <c r="DL6" s="5">
+      <c r="DM6" s="5">
         <v>800</v>
       </c>
-      <c r="DM6" s="5">
+      <c r="DN6" s="5">
         <v>850</v>
       </c>
-      <c r="DN6" s="5">
+      <c r="DO6" s="5">
         <v>900</v>
       </c>
-      <c r="DO6" s="5">
+      <c r="DP6" s="5">
         <v>950</v>
       </c>
-      <c r="DP6" s="5">
+      <c r="DQ6" s="5">
         <v>1000</v>
       </c>
-      <c r="DQ6" s="5">
+      <c r="DR6" s="5">
         <v>1050</v>
       </c>
-      <c r="DR6" s="5">
+      <c r="DS6" s="5">
         <v>1100</v>
       </c>
-      <c r="DS6" s="5">
+      <c r="DT6" s="5">
         <v>1150</v>
       </c>
-      <c r="DT6" s="5">
+      <c r="DU6" s="5">
         <v>1200</v>
       </c>
-      <c r="DU6" s="5">
+      <c r="DV6" s="5">
         <v>1250</v>
       </c>
-      <c r="DV6" s="5">
+      <c r="DW6" s="5">
         <v>1300</v>
       </c>
-      <c r="DW6" s="5">
+      <c r="DX6" s="5">
         <v>1350</v>
       </c>
-      <c r="DX6" s="5">
+      <c r="DY6" s="5">
         <v>1400</v>
       </c>
-      <c r="DY6" s="5">
+      <c r="DZ6" s="5">
         <v>1450</v>
       </c>
-      <c r="DZ6" s="5">
+      <c r="EA6" s="5">
         <v>1500</v>
       </c>
-      <c r="EA6" s="5"/>
       <c r="EB6" s="5"/>
       <c r="EC6" s="5"/>
       <c r="ED6" s="5"/>
@@ -11347,8 +14395,9 @@
       <c r="FE6" s="5"/>
       <c r="FF6" s="5"/>
       <c r="FG6" s="5"/>
+      <c r="FH6" s="5"/>
     </row>
-    <row r="7" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>48</v>
       </c>
@@ -11518,7 +14567,7 @@
         <v>9</v>
       </c>
       <c r="BE7" s="5" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="BF7" s="5" t="s">
         <v>9</v>
@@ -11536,7 +14585,7 @@
         <v>9</v>
       </c>
       <c r="BK7" s="5" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="BL7" s="5" t="s">
         <v>127</v>
@@ -11548,28 +14597,28 @@
         <v>127</v>
       </c>
       <c r="BO7" s="5" t="s">
-        <v>494</v>
+        <v>127</v>
       </c>
       <c r="BP7" s="5" t="s">
         <v>494</v>
       </c>
       <c r="BQ7" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="BR7" s="5" t="s">
         <v>495</v>
       </c>
       <c r="BS7" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="BT7" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="BT7" s="5" t="s">
-        <v>494</v>
       </c>
       <c r="BU7" s="5" t="s">
         <v>494</v>
       </c>
       <c r="BV7" s="5" t="s">
-        <v>127</v>
+        <v>494</v>
       </c>
       <c r="BW7" s="5" t="s">
         <v>127</v>
@@ -11578,7 +14627,7 @@
         <v>127</v>
       </c>
       <c r="BY7" s="5" t="s">
-        <v>494</v>
+        <v>127</v>
       </c>
       <c r="BZ7" s="5" t="s">
         <v>494</v>
@@ -11739,7 +14788,9 @@
       <c r="DZ7" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="EA7" s="5"/>
+      <c r="EA7" s="5" t="s">
+        <v>494</v>
+      </c>
       <c r="EB7" s="5"/>
       <c r="EC7" s="5"/>
       <c r="ED7" s="5"/>
@@ -11772,8 +14823,9 @@
       <c r="FE7" s="5"/>
       <c r="FF7" s="5"/>
       <c r="FG7" s="5"/>
+      <c r="FH7" s="5"/>
     </row>
-    <row r="8" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -11961,210 +15013,212 @@
         <v>1.52</v>
       </c>
       <c r="BK8" s="5">
+        <v>2.67</v>
+      </c>
+      <c r="BL8" s="5">
         <v>2.25</v>
       </c>
-      <c r="BL8" s="5">
+      <c r="BM8" s="5">
         <v>2.66</v>
       </c>
-      <c r="BM8" s="5">
+      <c r="BN8" s="5">
         <v>3.08</v>
       </c>
-      <c r="BN8" s="5">
+      <c r="BO8" s="5">
         <v>3.97</v>
       </c>
-      <c r="BO8" s="5">
+      <c r="BP8" s="5">
         <v>6.72</v>
       </c>
-      <c r="BP8" s="5">
+      <c r="BQ8" s="5">
         <v>8.93</v>
       </c>
-      <c r="BQ8" s="5">
+      <c r="BR8" s="5">
         <v>6.3</v>
       </c>
-      <c r="BR8" s="5">
+      <c r="BS8" s="5">
         <v>7.8</v>
       </c>
-      <c r="BS8" s="5">
+      <c r="BT8" s="5">
         <v>4.3899999999999997</v>
       </c>
-      <c r="BT8" s="5">
+      <c r="BU8" s="5">
         <v>5.91</v>
       </c>
-      <c r="BU8" s="5">
+      <c r="BV8" s="5">
         <v>7.51</v>
       </c>
-      <c r="BV8" s="5">
+      <c r="BW8" s="5">
         <v>2.81</v>
       </c>
-      <c r="BW8" s="5">
+      <c r="BX8" s="5">
         <v>3.28</v>
       </c>
-      <c r="BX8" s="5">
+      <c r="BY8" s="5">
         <v>4.01</v>
       </c>
-      <c r="BY8" s="5">
+      <c r="BZ8" s="5">
         <v>5.32</v>
       </c>
-      <c r="BZ8" s="5">
+      <c r="CA8" s="5">
         <v>7.26</v>
       </c>
-      <c r="CA8" s="5">
+      <c r="CB8" s="5">
         <v>9.26</v>
       </c>
-      <c r="CB8" s="5">
+      <c r="CC8" s="5">
         <v>11.35</v>
       </c>
-      <c r="CC8" s="5">
+      <c r="CD8" s="5">
         <v>12.15</v>
       </c>
-      <c r="CD8" s="5">
+      <c r="CE8" s="5">
         <v>14.82</v>
       </c>
-      <c r="CE8" s="5">
+      <c r="CF8" s="5">
         <v>16.239999999999998</v>
       </c>
-      <c r="CF8" s="5">
+      <c r="CG8" s="5">
         <v>16.52</v>
       </c>
-      <c r="CG8" s="5">
+      <c r="CH8" s="5">
         <v>18.52</v>
       </c>
-      <c r="CH8" s="5">
+      <c r="CI8" s="5">
         <v>20.61</v>
       </c>
-      <c r="CI8" s="5">
+      <c r="CJ8" s="5">
         <v>21.41</v>
       </c>
-      <c r="CJ8" s="5">
+      <c r="CK8" s="5">
         <v>23.5</v>
       </c>
-      <c r="CK8" s="5">
+      <c r="CL8" s="5">
         <v>26.17</v>
       </c>
-      <c r="CL8" s="5">
+      <c r="CM8" s="5">
         <v>26.97</v>
       </c>
-      <c r="CM8" s="5">
+      <c r="CN8" s="5">
         <v>29.64</v>
       </c>
-      <c r="CN8" s="5">
+      <c r="CO8" s="5">
         <v>31.06</v>
       </c>
-      <c r="CO8" s="5">
+      <c r="CP8" s="5">
         <v>32.479999999999997</v>
       </c>
-      <c r="CP8" s="5">
+      <c r="CQ8" s="5">
         <v>33.340000000000003</v>
       </c>
-      <c r="CQ8" s="5">
+      <c r="CR8" s="5">
         <v>34.76</v>
       </c>
-      <c r="CR8" s="5">
+      <c r="CS8" s="5">
         <v>37.520000000000003</v>
       </c>
-      <c r="CS8" s="5">
+      <c r="CT8" s="5">
         <v>38.32</v>
       </c>
-      <c r="CT8" s="5">
+      <c r="CU8" s="5">
         <v>40.99</v>
       </c>
-      <c r="CU8" s="5">
+      <c r="CV8" s="5">
         <v>41.79</v>
       </c>
-      <c r="CV8" s="5">
+      <c r="CW8" s="5">
         <v>44.46</v>
       </c>
-      <c r="CW8" s="5">
+      <c r="CX8" s="5">
         <v>45.88</v>
       </c>
-      <c r="CX8" s="5">
+      <c r="CY8" s="5">
         <v>47.3</v>
       </c>
-      <c r="CY8" s="5">
+      <c r="CZ8" s="5">
         <v>48.72</v>
       </c>
-      <c r="CZ8" s="5">
+      <c r="DA8" s="5">
         <v>5.65</v>
       </c>
-      <c r="DA8" s="5">
+      <c r="DB8" s="5">
         <v>7.09</v>
       </c>
-      <c r="DB8" s="5">
+      <c r="DC8" s="5">
         <v>9.9700000000000006</v>
       </c>
-      <c r="DC8" s="5">
+      <c r="DD8" s="5">
         <v>12.08</v>
       </c>
-      <c r="DD8" s="5">
+      <c r="DE8" s="5">
         <v>13.92</v>
       </c>
-      <c r="DE8" s="5">
+      <c r="DF8" s="5">
         <v>15.07</v>
       </c>
-      <c r="DF8" s="5">
+      <c r="DG8" s="5">
         <v>16.5</v>
       </c>
-      <c r="DG8" s="5">
+      <c r="DH8" s="5">
         <v>17.059999999999999</v>
       </c>
-      <c r="DH8" s="5">
+      <c r="DI8" s="5">
         <v>19.940000000000001</v>
       </c>
-      <c r="DI8" s="5">
+      <c r="DJ8" s="5">
         <v>22.05</v>
       </c>
-      <c r="DJ8" s="5">
+      <c r="DK8" s="5">
         <v>23.89</v>
       </c>
-      <c r="DK8" s="5">
+      <c r="DL8" s="5">
         <v>26</v>
       </c>
-      <c r="DL8" s="5">
+      <c r="DM8" s="5">
         <v>27.15</v>
       </c>
-      <c r="DM8" s="5">
+      <c r="DN8" s="5">
         <v>28.99</v>
       </c>
-      <c r="DN8" s="5">
+      <c r="DO8" s="5">
         <v>30.14</v>
       </c>
-      <c r="DO8" s="5">
+      <c r="DP8" s="5">
         <v>31.57</v>
       </c>
-      <c r="DP8" s="5">
+      <c r="DQ8" s="5">
         <v>33</v>
       </c>
-      <c r="DQ8" s="5">
+      <c r="DR8" s="5">
         <v>35.01</v>
       </c>
-      <c r="DR8" s="5">
+      <c r="DS8" s="5">
         <v>36.44</v>
       </c>
-      <c r="DS8" s="5">
+      <c r="DT8" s="5">
         <v>39.229999999999997</v>
       </c>
-      <c r="DT8" s="5">
+      <c r="DU8" s="5">
         <v>41.07</v>
       </c>
-      <c r="DU8" s="5">
+      <c r="DV8" s="5">
         <v>42.22</v>
       </c>
-      <c r="DV8" s="5">
+      <c r="DW8" s="5">
         <v>44.06</v>
       </c>
-      <c r="DW8" s="5">
+      <c r="DX8" s="5">
         <v>45.21</v>
       </c>
-      <c r="DX8" s="5">
+      <c r="DY8" s="5">
         <v>46.64</v>
       </c>
-      <c r="DY8" s="5">
+      <c r="DZ8" s="5">
         <v>48.07</v>
       </c>
-      <c r="DZ8" s="5">
+      <c r="EA8" s="5">
         <v>49.5</v>
       </c>
-      <c r="EA8" s="5"/>
       <c r="EB8" s="5"/>
       <c r="EC8" s="5"/>
       <c r="ED8" s="5"/>
@@ -12197,8 +15251,9 @@
       <c r="FE8" s="5"/>
       <c r="FF8" s="5"/>
       <c r="FG8" s="5"/>
+      <c r="FH8" s="5"/>
     </row>
-    <row r="9" spans="1:163" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:164" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
@@ -12386,10 +15441,10 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="BK9" s="5">
+        <v>16</v>
+      </c>
+      <c r="BL9" s="5">
         <v>20</v>
-      </c>
-      <c r="BL9" s="5">
-        <v>27</v>
       </c>
       <c r="BM9" s="5">
         <v>27</v>
@@ -12398,198 +15453,200 @@
         <v>27</v>
       </c>
       <c r="BO9" s="5">
+        <v>27</v>
+      </c>
+      <c r="BP9" s="5">
         <v>22</v>
       </c>
-      <c r="BP9" s="5">
+      <c r="BQ9" s="5">
         <v>24</v>
-      </c>
-      <c r="BQ9" s="5">
-        <v>26.5</v>
       </c>
       <c r="BR9" s="5">
         <v>26.5</v>
       </c>
       <c r="BS9" s="5">
+        <v>26.5</v>
+      </c>
+      <c r="BT9" s="5">
         <v>21.1</v>
-      </c>
-      <c r="BT9" s="5">
-        <v>18.5</v>
       </c>
       <c r="BU9" s="5">
         <v>18.5</v>
       </c>
       <c r="BV9" s="5">
+        <v>18.5</v>
+      </c>
+      <c r="BW9" s="5">
         <v>17.5</v>
-      </c>
-      <c r="BW9" s="5">
-        <v>27</v>
       </c>
       <c r="BX9" s="5">
         <v>27</v>
       </c>
       <c r="BY9" s="5">
+        <v>27</v>
+      </c>
+      <c r="BZ9" s="5">
         <v>16.100000000000001</v>
       </c>
-      <c r="BZ9" s="5">
+      <c r="CA9" s="5">
         <v>21.2</v>
       </c>
-      <c r="CA9" s="5">
+      <c r="CB9" s="5">
         <v>22.5</v>
       </c>
-      <c r="CB9" s="5">
+      <c r="CC9" s="5">
         <v>30.2</v>
       </c>
-      <c r="CC9" s="5">
+      <c r="CD9" s="5">
         <v>33.700000000000003</v>
       </c>
-      <c r="CD9" s="5">
+      <c r="CE9" s="5">
         <v>34.5</v>
       </c>
-      <c r="CE9" s="5">
+      <c r="CF9" s="5">
         <v>38.5</v>
       </c>
-      <c r="CF9" s="5">
+      <c r="CG9" s="5">
         <v>43.7</v>
       </c>
-      <c r="CG9" s="5">
+      <c r="CH9" s="5">
         <v>45</v>
       </c>
-      <c r="CH9" s="5">
+      <c r="CI9" s="5">
         <v>52.7</v>
       </c>
-      <c r="CI9" s="5">
+      <c r="CJ9" s="5">
         <v>56.2</v>
       </c>
-      <c r="CJ9" s="5">
+      <c r="CK9" s="5">
         <v>63.9</v>
       </c>
-      <c r="CK9" s="5">
+      <c r="CL9" s="5">
         <v>64.7</v>
       </c>
-      <c r="CL9" s="5">
+      <c r="CM9" s="5">
         <v>68.2</v>
       </c>
-      <c r="CM9" s="5">
+      <c r="CN9" s="5">
         <v>69</v>
       </c>
-      <c r="CN9" s="5">
+      <c r="CO9" s="5">
         <v>73</v>
       </c>
-      <c r="CO9" s="5">
+      <c r="CP9" s="5">
         <v>77</v>
       </c>
-      <c r="CP9" s="5">
+      <c r="CQ9" s="5">
         <v>79.5</v>
       </c>
-      <c r="CQ9" s="5">
+      <c r="CR9" s="5">
         <v>83.5</v>
       </c>
-      <c r="CR9" s="5">
+      <c r="CS9" s="5">
         <v>94.9</v>
       </c>
-      <c r="CS9" s="5">
+      <c r="CT9" s="5">
         <v>98.4</v>
       </c>
-      <c r="CT9" s="5">
+      <c r="CU9" s="5">
         <v>99.2</v>
       </c>
-      <c r="CU9" s="5">
+      <c r="CV9" s="5">
         <v>102.7</v>
       </c>
-      <c r="CV9" s="5">
+      <c r="CW9" s="5">
         <v>103.5</v>
       </c>
-      <c r="CW9" s="5">
+      <c r="CX9" s="5">
         <v>107.5</v>
       </c>
-      <c r="CX9" s="5">
+      <c r="CY9" s="5">
         <v>111.5</v>
       </c>
-      <c r="CY9" s="5">
+      <c r="CZ9" s="5">
         <v>115.5</v>
       </c>
-      <c r="CZ9" s="5">
+      <c r="DA9" s="5">
         <v>16.100000000000001</v>
       </c>
-      <c r="DA9" s="5">
+      <c r="DB9" s="5">
         <v>21.5</v>
       </c>
-      <c r="DB9" s="5">
+      <c r="DC9" s="5">
         <v>22.9</v>
       </c>
-      <c r="DC9" s="5">
+      <c r="DD9" s="5">
         <v>30.2</v>
       </c>
-      <c r="DD9" s="5">
+      <c r="DE9" s="5">
         <v>34</v>
       </c>
-      <c r="DE9" s="5">
+      <c r="DF9" s="5">
         <v>34.700000000000003</v>
       </c>
-      <c r="DF9" s="5">
+      <c r="DG9" s="5">
         <v>39.700000000000003</v>
       </c>
-      <c r="DG9" s="5">
+      <c r="DH9" s="5">
         <v>44.4</v>
       </c>
-      <c r="DH9" s="5">
+      <c r="DI9" s="5">
         <v>45.8</v>
       </c>
-      <c r="DI9" s="5">
+      <c r="DJ9" s="5">
         <v>53.1</v>
       </c>
-      <c r="DJ9" s="5">
+      <c r="DK9" s="5">
         <v>56.9</v>
       </c>
-      <c r="DK9" s="5">
+      <c r="DL9" s="5">
         <v>64.2</v>
       </c>
-      <c r="DL9" s="5">
+      <c r="DM9" s="5">
         <v>64.900000000000006</v>
       </c>
-      <c r="DM9" s="5">
+      <c r="DN9" s="5">
         <v>68.7</v>
       </c>
-      <c r="DN9" s="5">
+      <c r="DO9" s="5">
         <v>69.400000000000006</v>
       </c>
-      <c r="DO9" s="5">
+      <c r="DP9" s="5">
         <v>74.400000000000006</v>
       </c>
-      <c r="DP9" s="5">
+      <c r="DQ9" s="5">
         <v>79.400000000000006</v>
       </c>
-      <c r="DQ9" s="5">
+      <c r="DR9" s="5">
         <v>80.5</v>
       </c>
-      <c r="DR9" s="5">
+      <c r="DS9" s="5">
         <v>85.5</v>
       </c>
-      <c r="DS9" s="5">
+      <c r="DT9" s="5">
         <v>95.1</v>
       </c>
-      <c r="DT9" s="5">
+      <c r="DU9" s="5">
         <v>98.9</v>
       </c>
-      <c r="DU9" s="5">
+      <c r="DV9" s="5">
         <v>99.6</v>
       </c>
-      <c r="DV9" s="5">
+      <c r="DW9" s="5">
         <v>103.4</v>
       </c>
-      <c r="DW9" s="5">
+      <c r="DX9" s="5">
         <v>104.1</v>
       </c>
-      <c r="DX9" s="5">
+      <c r="DY9" s="5">
         <v>109.1</v>
       </c>
-      <c r="DY9" s="5">
+      <c r="DZ9" s="5">
         <v>114.1</v>
       </c>
-      <c r="DZ9" s="5">
+      <c r="EA9" s="5">
         <v>119.1</v>
       </c>
-      <c r="EA9" s="5"/>
       <c r="EB9" s="5"/>
       <c r="EC9" s="5"/>
       <c r="ED9" s="5"/>
@@ -12622,8 +15679,9 @@
       <c r="FE9" s="5"/>
       <c r="FF9" s="5"/>
       <c r="FG9" s="5"/>
+      <c r="FH9" s="5"/>
     </row>
-    <row r="10" spans="1:163" ht="25.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:164" ht="25.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -12807,10 +15865,10 @@
         <v>10</v>
       </c>
       <c r="BK10" s="5">
+        <v>20</v>
+      </c>
+      <c r="BL10" s="5">
         <v>25</v>
-      </c>
-      <c r="BL10" s="5">
-        <v>30</v>
       </c>
       <c r="BM10" s="5">
         <v>30</v>
@@ -12819,10 +15877,10 @@
         <v>30</v>
       </c>
       <c r="BO10" s="5">
+        <v>30</v>
+      </c>
+      <c r="BP10" s="5">
         <v>25</v>
-      </c>
-      <c r="BP10" s="5">
-        <v>30</v>
       </c>
       <c r="BQ10" s="5">
         <v>30</v>
@@ -12834,7 +15892,7 @@
         <v>30</v>
       </c>
       <c r="BT10" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BU10" s="5">
         <v>25</v>
@@ -12843,46 +15901,46 @@
         <v>25</v>
       </c>
       <c r="BW10" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BX10" s="5">
         <v>30</v>
       </c>
       <c r="BY10" s="5">
+        <v>30</v>
+      </c>
+      <c r="BZ10" s="5">
         <v>20</v>
-      </c>
-      <c r="BZ10" s="5">
-        <v>25</v>
       </c>
       <c r="CA10" s="5">
         <v>25</v>
       </c>
       <c r="CB10" s="5">
+        <v>25</v>
+      </c>
+      <c r="CC10" s="5">
         <v>35</v>
-      </c>
-      <c r="CC10" s="5">
-        <v>40</v>
       </c>
       <c r="CD10" s="5">
         <v>40</v>
       </c>
       <c r="CE10" s="5">
+        <v>40</v>
+      </c>
+      <c r="CF10" s="5">
         <v>45</v>
-      </c>
-      <c r="CF10" s="5">
-        <v>50</v>
       </c>
       <c r="CG10" s="5">
         <v>50</v>
       </c>
       <c r="CH10" s="5">
+        <v>50</v>
+      </c>
+      <c r="CI10" s="5">
         <v>60</v>
       </c>
-      <c r="CI10" s="5">
+      <c r="CJ10" s="5">
         <v>70</v>
-      </c>
-      <c r="CJ10" s="5">
-        <v>80</v>
       </c>
       <c r="CK10" s="5">
         <v>80</v>
@@ -12894,7 +15952,7 @@
         <v>80</v>
       </c>
       <c r="CN10" s="5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="CO10" s="5">
         <v>90</v>
@@ -12903,10 +15961,10 @@
         <v>90</v>
       </c>
       <c r="CQ10" s="5">
+        <v>90</v>
+      </c>
+      <c r="CR10" s="5">
         <v>100</v>
-      </c>
-      <c r="CR10" s="5">
-        <v>110</v>
       </c>
       <c r="CS10" s="5">
         <v>110</v>
@@ -12915,7 +15973,7 @@
         <v>110</v>
       </c>
       <c r="CU10" s="5">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="CV10" s="5">
         <v>125</v>
@@ -12927,43 +15985,43 @@
         <v>125</v>
       </c>
       <c r="CY10" s="5">
+        <v>125</v>
+      </c>
+      <c r="CZ10" s="5">
         <v>150</v>
       </c>
-      <c r="CZ10" s="5">
+      <c r="DA10" s="5">
         <v>20</v>
       </c>
-      <c r="DA10" s="5">
+      <c r="DB10" s="5">
         <v>25</v>
       </c>
-      <c r="DB10" s="5">
+      <c r="DC10" s="5">
         <v>30</v>
       </c>
-      <c r="DC10" s="5">
+      <c r="DD10" s="5">
         <v>35</v>
-      </c>
-      <c r="DD10" s="5">
-        <v>40</v>
       </c>
       <c r="DE10" s="5">
         <v>40</v>
       </c>
       <c r="DF10" s="5">
+        <v>40</v>
+      </c>
+      <c r="DG10" s="5">
         <v>45</v>
       </c>
-      <c r="DG10" s="5">
+      <c r="DH10" s="5">
         <v>50</v>
-      </c>
-      <c r="DH10" s="5">
-        <v>60</v>
       </c>
       <c r="DI10" s="5">
         <v>60</v>
       </c>
       <c r="DJ10" s="5">
+        <v>60</v>
+      </c>
+      <c r="DK10" s="5">
         <v>70</v>
-      </c>
-      <c r="DK10" s="5">
-        <v>80</v>
       </c>
       <c r="DL10" s="5">
         <v>80</v>
@@ -12975,7 +16033,7 @@
         <v>80</v>
       </c>
       <c r="DO10" s="5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="DP10" s="5">
         <v>90</v>
@@ -12984,10 +16042,10 @@
         <v>90</v>
       </c>
       <c r="DR10" s="5">
+        <v>90</v>
+      </c>
+      <c r="DS10" s="5">
         <v>100</v>
-      </c>
-      <c r="DS10" s="5">
-        <v>110</v>
       </c>
       <c r="DT10" s="5">
         <v>110</v>
@@ -12996,7 +16054,7 @@
         <v>110</v>
       </c>
       <c r="DV10" s="5">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="DW10" s="5">
         <v>125</v>
@@ -13005,12 +16063,14 @@
         <v>125</v>
       </c>
       <c r="DY10" s="5">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="DZ10" s="5">
         <v>150</v>
       </c>
-      <c r="EA10" s="5"/>
+      <c r="EA10" s="5">
+        <v>150</v>
+      </c>
       <c r="EB10" s="5"/>
       <c r="EC10" s="5"/>
       <c r="ED10" s="5"/>
@@ -13043,8 +16103,9 @@
       <c r="FE10" s="5"/>
       <c r="FF10" s="5"/>
       <c r="FG10" s="5"/>
+      <c r="FH10" s="5"/>
     </row>
-    <row r="11" spans="1:163" ht="25.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:164" ht="25.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>58</v>
       </c>
@@ -13229,8 +16290,8 @@
       <c r="BJ11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="BK11" s="15">
-        <v>40</v>
+      <c r="BK11" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="BL11" s="15">
         <v>40</v>
@@ -13241,8 +16302,8 @@
       <c r="BN11" s="15">
         <v>40</v>
       </c>
-      <c r="BO11" s="15" t="s">
-        <v>37</v>
+      <c r="BO11" s="15">
+        <v>40</v>
       </c>
       <c r="BP11" s="15" t="s">
         <v>37</v>
@@ -13271,8 +16332,8 @@
       <c r="BX11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="BY11" s="15">
-        <v>78.400000000000006</v>
+      <c r="BY11" s="15" t="s">
+        <v>37</v>
       </c>
       <c r="BZ11" s="15">
         <v>78.400000000000006</v>
@@ -13433,7 +16494,9 @@
       <c r="DZ11" s="15">
         <v>78.400000000000006</v>
       </c>
-      <c r="EA11" s="15"/>
+      <c r="EA11" s="15">
+        <v>78.400000000000006</v>
+      </c>
       <c r="EB11" s="15"/>
       <c r="EC11" s="15"/>
       <c r="ED11" s="15"/>
@@ -13466,8 +16529,9 @@
       <c r="FE11" s="15"/>
       <c r="FF11" s="15"/>
       <c r="FG11" s="15"/>
+      <c r="FH11" s="15"/>
     </row>
-    <row r="12" spans="1:163" ht="60" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:164" ht="60" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>51</v>
       </c>
@@ -13655,7 +16719,7 @@
         <v>40</v>
       </c>
       <c r="BK12" s="15" t="s">
-        <v>125</v>
+        <v>570</v>
       </c>
       <c r="BL12" s="15" t="s">
         <v>125</v>
@@ -13667,13 +16731,13 @@
         <v>125</v>
       </c>
       <c r="BO12" s="15" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="BP12" s="15" t="s">
         <v>143</v>
       </c>
       <c r="BQ12" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BR12" s="15" t="s">
         <v>144</v>
@@ -13688,7 +16752,7 @@
         <v>144</v>
       </c>
       <c r="BV12" s="15" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="BW12" s="15" t="s">
         <v>74</v>
@@ -13697,7 +16761,7 @@
         <v>74</v>
       </c>
       <c r="BY12" s="15" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
       <c r="BZ12" s="15" t="s">
         <v>177</v>
@@ -13706,7 +16770,7 @@
         <v>177</v>
       </c>
       <c r="CB12" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="CC12" s="15" t="s">
         <v>178</v>
@@ -13718,43 +16782,43 @@
         <v>178</v>
       </c>
       <c r="CF12" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="CG12" s="15" t="s">
         <v>179</v>
       </c>
       <c r="CH12" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="CI12" s="15" t="s">
         <v>180</v>
       </c>
       <c r="CJ12" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="CK12" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="CK12" s="15" t="s">
+      <c r="CL12" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="CL12" s="15" t="s">
+      <c r="CM12" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="CM12" s="15" t="s">
+      <c r="CN12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="CN12" s="15" t="s">
+      <c r="CO12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="CO12" s="15" t="s">
+      <c r="CP12" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="CP12" s="15" t="s">
+      <c r="CQ12" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="CQ12" s="15" t="s">
+      <c r="CR12" s="15" t="s">
         <v>188</v>
-      </c>
-      <c r="CR12" s="15" t="s">
-        <v>189</v>
       </c>
       <c r="CS12" s="15" t="s">
         <v>189</v>
@@ -13778,7 +16842,7 @@
         <v>189</v>
       </c>
       <c r="CZ12" s="15" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="DA12" s="15" t="s">
         <v>177</v>
@@ -13787,7 +16851,7 @@
         <v>177</v>
       </c>
       <c r="DC12" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="DD12" s="15" t="s">
         <v>178</v>
@@ -13799,43 +16863,43 @@
         <v>178</v>
       </c>
       <c r="DG12" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="DH12" s="15" t="s">
         <v>179</v>
       </c>
       <c r="DI12" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="DJ12" s="15" t="s">
         <v>180</v>
       </c>
       <c r="DK12" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="DL12" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="DL12" s="15" t="s">
+      <c r="DM12" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="DM12" s="15" t="s">
+      <c r="DN12" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="DN12" s="15" t="s">
+      <c r="DO12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="DO12" s="15" t="s">
+      <c r="DP12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="DP12" s="15" t="s">
+      <c r="DQ12" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="DQ12" s="15" t="s">
+      <c r="DR12" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="DR12" s="15" t="s">
+      <c r="DS12" s="15" t="s">
         <v>188</v>
-      </c>
-      <c r="DS12" s="15" t="s">
-        <v>189</v>
       </c>
       <c r="DT12" s="15" t="s">
         <v>189</v>
@@ -13858,7 +16922,9 @@
       <c r="DZ12" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="EA12" s="15"/>
+      <c r="EA12" s="15" t="s">
+        <v>189</v>
+      </c>
       <c r="EB12" s="15"/>
       <c r="EC12" s="15"/>
       <c r="ED12" s="15"/>
@@ -13889,12 +16955,13 @@
       <c r="FC12" s="15"/>
       <c r="FD12" s="15"/>
       <c r="FE12" s="15"/>
+      <c r="FF12" s="15"/>
     </row>
-    <row r="13" spans="1:163" ht="25.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:164" ht="25.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="25" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -14088,7 +17155,7 @@
         <v>56</v>
       </c>
       <c r="BO13" s="12" t="s">
-        <v>145</v>
+        <v>56</v>
       </c>
       <c r="BP13" s="12" t="s">
         <v>145</v>
@@ -14109,7 +17176,7 @@
         <v>145</v>
       </c>
       <c r="BV13" s="12" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="BW13" s="12" t="s">
         <v>56</v>
@@ -14118,7 +17185,7 @@
         <v>56</v>
       </c>
       <c r="BY13" s="12" t="s">
-        <v>538</v>
+        <v>56</v>
       </c>
       <c r="BZ13" s="12" t="s">
         <v>538</v>
@@ -14199,7 +17266,7 @@
         <v>538</v>
       </c>
       <c r="CZ13" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="DA13" s="12" t="s">
         <v>539</v>
@@ -14279,7 +17346,9 @@
       <c r="DZ13" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="EA13" s="12"/>
+      <c r="EA13" s="12" t="s">
+        <v>539</v>
+      </c>
       <c r="EB13" s="12"/>
       <c r="EC13" s="12"/>
       <c r="ED13" s="12"/>
@@ -14312,6 +17381,621 @@
       <c r="FE13" s="12"/>
       <c r="FF13" s="12"/>
       <c r="FG13" s="12"/>
+      <c r="FH13" s="12"/>
+    </row>
+    <row r="14" spans="1:164" ht="25.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="S14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="T14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="U14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="W14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="X14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AR14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AT14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AU14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AV14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AX14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AY14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AZ14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BA14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BB14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BC14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BD14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BE14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BF14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BH14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BI14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BJ14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BK14" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="BL14" s="21"/>
+      <c r="BM14" s="21"/>
+      <c r="BN14" s="21"/>
+      <c r="BO14" s="21"/>
+      <c r="BP14" s="21"/>
+      <c r="BQ14" s="21"/>
+      <c r="BR14" s="21"/>
+      <c r="BS14" s="21"/>
+      <c r="BT14" s="21"/>
+      <c r="BU14" s="21"/>
+      <c r="BV14" s="21"/>
+      <c r="BW14" s="21"/>
+      <c r="BX14" s="21"/>
+      <c r="BY14" s="21"/>
+      <c r="BZ14" s="21"/>
+      <c r="CA14" s="21"/>
+      <c r="CB14" s="21"/>
+      <c r="CC14" s="21"/>
+      <c r="CD14" s="21"/>
+      <c r="CE14" s="21"/>
+      <c r="CF14" s="21"/>
+      <c r="CG14" s="21"/>
+      <c r="CH14" s="21"/>
+      <c r="CI14" s="21"/>
+      <c r="CJ14" s="21"/>
+      <c r="CK14" s="21"/>
+      <c r="CL14" s="21"/>
+      <c r="CM14" s="21"/>
+      <c r="CN14" s="21"/>
+      <c r="CO14" s="21"/>
+      <c r="CP14" s="21"/>
+      <c r="CQ14" s="21"/>
+      <c r="CR14" s="21"/>
+      <c r="CS14" s="21"/>
+      <c r="CT14" s="21"/>
+      <c r="CU14" s="21"/>
+      <c r="CV14" s="21"/>
+      <c r="CW14" s="21"/>
+      <c r="CX14" s="21"/>
+      <c r="CY14" s="21"/>
+      <c r="CZ14" s="21"/>
+      <c r="DA14" s="21"/>
+      <c r="DB14" s="21"/>
+      <c r="DC14" s="21"/>
+      <c r="DD14" s="21"/>
+      <c r="DE14" s="21"/>
+      <c r="DF14" s="21"/>
+      <c r="DG14" s="21"/>
+      <c r="DH14" s="21"/>
+      <c r="DI14" s="21"/>
+      <c r="DJ14" s="21"/>
+      <c r="DK14" s="21"/>
+      <c r="DL14" s="21"/>
+      <c r="DM14" s="21"/>
+      <c r="DN14" s="21"/>
+      <c r="DO14" s="21"/>
+      <c r="DP14" s="21"/>
+      <c r="DQ14" s="21"/>
+      <c r="DR14" s="21"/>
+      <c r="DS14" s="21"/>
+      <c r="DT14" s="21"/>
+      <c r="DU14" s="21"/>
+      <c r="DV14" s="21"/>
+      <c r="DW14" s="21"/>
+      <c r="DX14" s="21"/>
+      <c r="DY14" s="21"/>
+      <c r="DZ14" s="21"/>
+      <c r="EA14" s="21"/>
+      <c r="EB14" s="21"/>
+      <c r="EC14" s="21"/>
+      <c r="ED14" s="21"/>
+      <c r="EE14" s="21"/>
+      <c r="EF14" s="21"/>
+      <c r="EG14" s="21"/>
+      <c r="EH14" s="21"/>
+      <c r="EI14" s="21"/>
+      <c r="EJ14" s="21"/>
+      <c r="EK14" s="21"/>
+      <c r="EL14" s="21"/>
+      <c r="EM14" s="21"/>
+      <c r="EN14" s="21"/>
+      <c r="EO14" s="21"/>
+      <c r="EP14" s="21"/>
+      <c r="EQ14" s="21"/>
+      <c r="ER14" s="21"/>
+      <c r="ES14" s="21"/>
+      <c r="ET14" s="21"/>
+      <c r="EU14" s="21"/>
+      <c r="EV14" s="21"/>
+      <c r="EW14" s="21"/>
+      <c r="EX14" s="21"/>
+      <c r="EY14" s="21"/>
+      <c r="EZ14" s="21"/>
+      <c r="FA14" s="21"/>
+      <c r="FB14" s="21"/>
+      <c r="FC14" s="21"/>
+      <c r="FD14" s="21"/>
+      <c r="FE14" s="21"/>
+      <c r="FF14" s="21"/>
+      <c r="FG14" s="21"/>
+      <c r="FH14" s="21"/>
+    </row>
+    <row r="15" spans="1:164" s="56" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="52" t="s">
+        <v>562</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="53">
+        <v>28000</v>
+      </c>
+      <c r="D15" s="54" t="s">
+        <v>564</v>
+      </c>
+      <c r="E15" s="55">
+        <v>20600</v>
+      </c>
+      <c r="F15" s="56">
+        <v>23800</v>
+      </c>
+      <c r="G15" s="56">
+        <v>25100</v>
+      </c>
+      <c r="H15" s="56">
+        <v>30000</v>
+      </c>
+      <c r="I15" s="56">
+        <v>34260</v>
+      </c>
+      <c r="J15" s="56">
+        <v>39960</v>
+      </c>
+      <c r="K15" s="56">
+        <v>44460</v>
+      </c>
+      <c r="L15" s="56">
+        <v>51660</v>
+      </c>
+      <c r="M15" s="56">
+        <v>56660</v>
+      </c>
+      <c r="N15" s="56">
+        <v>26500</v>
+      </c>
+      <c r="O15" s="56">
+        <v>29700</v>
+      </c>
+      <c r="P15" s="56">
+        <v>32700</v>
+      </c>
+      <c r="Q15" s="56">
+        <v>35400</v>
+      </c>
+      <c r="R15" s="56">
+        <v>39460</v>
+      </c>
+      <c r="S15" s="56">
+        <v>44960</v>
+      </c>
+      <c r="T15" s="56">
+        <v>47660</v>
+      </c>
+      <c r="AD15" s="56">
+        <v>19700</v>
+      </c>
+      <c r="AE15" s="56">
+        <v>22600</v>
+      </c>
+      <c r="AF15" s="56">
+        <v>24300</v>
+      </c>
+      <c r="AG15" s="56">
+        <v>27800</v>
+      </c>
+      <c r="AH15" s="56">
+        <v>33360</v>
+      </c>
+      <c r="AI15" s="56">
+        <v>37960</v>
+      </c>
+      <c r="AJ15" s="56">
+        <v>41960</v>
+      </c>
+      <c r="AR15" s="56">
+        <v>17800</v>
+      </c>
+      <c r="AS15" s="56">
+        <v>19700</v>
+      </c>
+      <c r="AT15" s="56">
+        <v>21400</v>
+      </c>
+      <c r="AU15" s="56">
+        <v>25500</v>
+      </c>
+      <c r="AV15" s="56">
+        <v>32660</v>
+      </c>
+      <c r="AW15" s="56">
+        <v>36860</v>
+      </c>
+      <c r="AX15" s="56">
+        <v>40860</v>
+      </c>
+      <c r="BF15" s="56">
+        <v>52780</v>
+      </c>
+      <c r="BG15" s="56">
+        <v>71780</v>
+      </c>
+      <c r="BH15" s="56">
+        <v>87180</v>
+      </c>
+      <c r="BI15" s="56">
+        <v>99180</v>
+      </c>
+      <c r="BJ15" s="56">
+        <v>41780</v>
+      </c>
+      <c r="BK15" s="56">
+        <v>74780</v>
+      </c>
+      <c r="BL15" s="56">
+        <v>115000</v>
+      </c>
+      <c r="BM15" s="56">
+        <v>131000</v>
+      </c>
+      <c r="BN15" s="56">
+        <v>147000</v>
+      </c>
+      <c r="BO15" s="56">
+        <v>188000</v>
+      </c>
+      <c r="BP15" s="56">
+        <v>282000</v>
+      </c>
+      <c r="BQ15" s="56">
+        <v>330000</v>
+      </c>
+      <c r="BR15" s="56">
+        <v>190000</v>
+      </c>
+      <c r="BS15" s="56">
+        <v>219000</v>
+      </c>
+      <c r="BT15" s="56">
+        <v>173000</v>
+      </c>
+      <c r="BU15" s="56">
+        <v>197000</v>
+      </c>
+      <c r="BV15" s="56">
+        <v>224000</v>
+      </c>
+      <c r="BW15" s="56">
+        <v>110500</v>
+      </c>
+      <c r="BX15" s="56">
+        <v>125800</v>
+      </c>
+      <c r="BY15" s="56">
+        <v>141100</v>
+      </c>
+      <c r="BZ15" s="56">
+        <v>235600</v>
+      </c>
+      <c r="CA15" s="56">
+        <v>28900</v>
+      </c>
+      <c r="CB15" s="56">
+        <v>33900</v>
+      </c>
+      <c r="CC15" s="56">
+        <v>390500</v>
+      </c>
+      <c r="CD15" s="56">
+        <v>443500</v>
+      </c>
+      <c r="CE15" s="56">
+        <v>497500</v>
+      </c>
+      <c r="CF15" s="56">
+        <v>547300</v>
+      </c>
+      <c r="CG15" s="56">
+        <v>628000</v>
+      </c>
+      <c r="CH15" s="56">
+        <v>678000</v>
+      </c>
+      <c r="CI15" s="56">
+        <v>729500</v>
+      </c>
+      <c r="CJ15" s="56">
+        <v>782500</v>
+      </c>
+      <c r="CK15" s="56">
+        <v>834000</v>
+      </c>
+      <c r="CL15" s="56">
+        <v>888000</v>
+      </c>
+      <c r="CM15" s="56">
+        <v>941000</v>
+      </c>
+      <c r="CN15" s="56">
+        <v>995000</v>
+      </c>
+      <c r="CO15" s="56">
+        <v>1044800</v>
+      </c>
+      <c r="CP15" s="56">
+        <v>1094600</v>
+      </c>
+      <c r="CQ15" s="56">
+        <v>1175500</v>
+      </c>
+      <c r="CR15" s="56">
+        <v>1225300</v>
+      </c>
+      <c r="CS15" s="56">
+        <v>1278500</v>
+      </c>
+      <c r="CT15" s="56">
+        <v>1331500</v>
+      </c>
+      <c r="CU15" s="56">
+        <v>1385500</v>
+      </c>
+      <c r="CV15" s="56">
+        <v>1438500</v>
+      </c>
+      <c r="CW15" s="56">
+        <v>1492500</v>
+      </c>
+      <c r="CX15" s="56">
+        <v>1542300</v>
+      </c>
+      <c r="CY15" s="56">
+        <v>1592100</v>
+      </c>
+      <c r="CZ15" s="56">
+        <v>1641900</v>
+      </c>
+      <c r="DA15" s="56">
+        <v>282000</v>
+      </c>
+      <c r="DB15" s="56">
+        <v>346000</v>
+      </c>
+      <c r="DC15" s="56">
+        <v>406000</v>
+      </c>
+      <c r="DD15" s="56">
+        <v>469500</v>
+      </c>
+      <c r="DE15" s="56">
+        <v>529500</v>
+      </c>
+      <c r="DF15" s="56">
+        <v>595500</v>
+      </c>
+      <c r="DG15" s="56">
+        <v>655300</v>
+      </c>
+      <c r="DH15" s="56">
+        <v>752000</v>
+      </c>
+      <c r="DI15" s="56">
+        <v>812000</v>
+      </c>
+      <c r="DJ15" s="56">
+        <v>875500</v>
+      </c>
+      <c r="DK15" s="56">
+        <v>935500</v>
+      </c>
+      <c r="DL15" s="56">
+        <v>999000</v>
+      </c>
+      <c r="DM15" s="56">
+        <v>1065000</v>
+      </c>
+      <c r="DN15" s="56">
+        <v>1125000</v>
+      </c>
+      <c r="DO15" s="56">
+        <v>1191000</v>
+      </c>
+      <c r="DP15" s="56">
+        <v>1250800</v>
+      </c>
+      <c r="DQ15" s="56">
+        <v>1310600</v>
+      </c>
+      <c r="DR15" s="56">
+        <v>1407500</v>
+      </c>
+      <c r="DS15" s="56">
+        <v>1467300</v>
+      </c>
+      <c r="DT15" s="56">
+        <v>1534500</v>
+      </c>
+      <c r="DU15" s="56">
+        <v>1594500</v>
+      </c>
+      <c r="DV15" s="56">
+        <v>1660500</v>
+      </c>
+      <c r="DW15" s="56">
+        <v>1720500</v>
+      </c>
+      <c r="DX15" s="56">
+        <v>1786500</v>
+      </c>
+      <c r="DY15" s="56">
+        <v>1846300</v>
+      </c>
+      <c r="DZ15" s="56">
+        <v>1906100</v>
+      </c>
+      <c r="EA15" s="56">
+        <v>1965900</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -14320,9 +18004,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB764343-28B8-406D-977B-66BB2AAB408D}">
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.109375" style="2" customWidth="1"/>
@@ -15431,6 +19115,416 @@
       </c>
       <c r="AF12" s="9"/>
     </row>
+    <row r="13" spans="1:32" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+    </row>
+    <row r="14" spans="1:32" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>540</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="E14" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="T14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="U14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="V14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="W14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="X14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD14" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE14" s="29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="E15" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>551</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="L15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="M15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="O15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="S15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="T15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="U15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="V15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="W15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="X15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="Y15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="Z15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AA15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AB15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AC15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AD15" s="29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AE15" s="29" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" customFormat="1" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="E16" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>560</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="P16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="T16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="U16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="V16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="W16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="X16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD16" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE16" s="29" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A18" s="24" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A19" s="24" t="s">
+        <v>568</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15438,9 +19532,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416E1F1A-25CB-4357-AA92-79D3362290DE}">
-  <dimension ref="A1:BL14"/>
+  <dimension ref="A1:BL17"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="1"/>
@@ -17114,6 +21208,30 @@
       <c r="BK14" s="21"/>
       <c r="BL14" s="21"/>
     </row>
+    <row r="15" spans="1:64" s="51" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="47" t="s">
+        <v>562</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="50" t="s">
+        <v>566</v>
+      </c>
+      <c r="E15" s="51">
+        <v>61980</v>
+      </c>
+      <c r="F15" s="51">
+        <v>87980</v>
+      </c>
+    </row>
+    <row r="16" spans="1:64" x14ac:dyDescent="0.3">
+      <c r="A16" s="24"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="24"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/EQUIPMENT_Data.xlsx
+++ b/EQUIPMENT_Data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9EF483C-5E4C-4DCA-A613-CC50AFC93250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20AE930-581C-456C-89EE-64F8ED51DB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7596" yWindow="168" windowWidth="15504" windowHeight="12240" xr2:uid="{B9AE4098-F0A1-4C76-B9D5-37F1BE2208A4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{B9AE4098-F0A1-4C76-B9D5-37F1BE2208A4}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_units" sheetId="1" r:id="rId1"/>
-    <sheet name="controller" sheetId="5" r:id="rId2"/>
+    <sheet name="controller&amp;pipe" sheetId="5" r:id="rId2"/>
     <sheet name="outdoor_units" sheetId="2" r:id="rId3"/>
     <sheet name="indoor_units_SA only" sheetId="3" r:id="rId4"/>
     <sheet name="outdoor_units_SA only" sheetId="4" r:id="rId5"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="634">
   <si>
     <t>資料型態</t>
   </si>
@@ -2395,6 +2395,50 @@
   </si>
   <si>
     <t>RHF40VAVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCPH01H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>含Z-wave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伶俐智控管理器-住宅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VRV分歧頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KHRP26A22T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KHRP26A33T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KHRP26A72T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KHRP26A73T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>室內機分歧頭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BHFP22P100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BHFP22P151</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -12121,7 +12165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F00506A-09F5-4009-80F2-281B4A4C3425}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -12132,9 +12176,12 @@
     <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.44140625" customWidth="1"/>
     <col min="12" max="12" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>569</v>
       </c>
@@ -12147,8 +12194,14 @@
       <c r="L1" t="s">
         <v>612</v>
       </c>
+      <c r="O1" t="s">
+        <v>557</v>
+      </c>
+      <c r="R1" t="s">
+        <v>626</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>605</v>
       </c>
@@ -12179,8 +12232,23 @@
       <c r="M2" t="s">
         <v>607</v>
       </c>
+      <c r="O2" t="s">
+        <v>605</v>
+      </c>
+      <c r="P2" t="s">
+        <v>607</v>
+      </c>
+      <c r="R2" t="s">
+        <v>605</v>
+      </c>
+      <c r="S2" t="s">
+        <v>607</v>
+      </c>
+      <c r="T2" t="s">
+        <v>610</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="61" t="s">
         <v>570</v>
       </c>
@@ -12211,8 +12279,23 @@
       <c r="M3">
         <v>4500</v>
       </c>
+      <c r="O3" t="s">
+        <v>561</v>
+      </c>
+      <c r="P3">
+        <v>4500</v>
+      </c>
+      <c r="R3" t="s">
+        <v>627</v>
+      </c>
+      <c r="S3">
+        <v>1700</v>
+      </c>
+      <c r="T3" t="s">
+        <v>631</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="61" t="s">
         <v>573</v>
       </c>
@@ -12237,8 +12320,17 @@
       <c r="J4">
         <v>1600</v>
       </c>
+      <c r="R4" t="s">
+        <v>628</v>
+      </c>
+      <c r="S4">
+        <v>2400</v>
+      </c>
+      <c r="T4" t="s">
+        <v>631</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>581</v>
       </c>
@@ -12254,8 +12346,17 @@
       <c r="J5">
         <v>1600</v>
       </c>
+      <c r="R5" t="s">
+        <v>629</v>
+      </c>
+      <c r="S5">
+        <v>3300</v>
+      </c>
+      <c r="T5" t="s">
+        <v>631</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="61" t="s">
         <v>574</v>
       </c>
@@ -12268,8 +12369,17 @@
       <c r="D6" t="s">
         <v>609</v>
       </c>
+      <c r="R6" t="s">
+        <v>630</v>
+      </c>
+      <c r="S6">
+        <v>4600</v>
+      </c>
+      <c r="T6" t="s">
+        <v>631</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>575</v>
       </c>
@@ -12279,8 +12389,17 @@
       <c r="C7">
         <v>7350</v>
       </c>
+      <c r="R7" t="s">
+        <v>632</v>
+      </c>
+      <c r="S7">
+        <v>3700</v>
+      </c>
+      <c r="T7" t="s">
+        <v>533</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="61" t="s">
         <v>578</v>
       </c>
@@ -12293,8 +12412,17 @@
       <c r="D8" t="s">
         <v>609</v>
       </c>
+      <c r="R8" t="s">
+        <v>633</v>
+      </c>
+      <c r="S8">
+        <v>7500</v>
+      </c>
+      <c r="T8" t="s">
+        <v>533</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>579</v>
       </c>
@@ -12305,7 +12433,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="61" t="s">
         <v>584</v>
       </c>
@@ -12320,7 +12448,7 @@
       </c>
       <c r="F10" s="62"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>586</v>
       </c>
@@ -12331,7 +12459,7 @@
         <v>28600</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>588</v>
       </c>
@@ -12342,7 +12470,7 @@
         <v>19400</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>591</v>
       </c>
@@ -12356,7 +12484,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>590</v>
       </c>
@@ -12367,7 +12495,7 @@
         <v>27500</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="61" t="s">
         <v>594</v>
       </c>
@@ -12381,7 +12509,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="61" t="s">
         <v>598</v>
       </c>
@@ -12429,6 +12557,21 @@
       </c>
       <c r="D19" t="s">
         <v>609</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="61" t="s">
+        <v>623</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>625</v>
+      </c>
+      <c r="C20">
+        <f>25350+2350</f>
+        <v>27700</v>
+      </c>
+      <c r="D20" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/EQUIPMENT_Data.xlsx
+++ b/EQUIPMENT_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20AE930-581C-456C-89EE-64F8ED51DB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F125FE-6683-4CB1-A754-0C15F49963FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{B9AE4098-F0A1-4C76-B9D5-37F1BE2208A4}"/>
+    <workbookView xWindow="2028" yWindow="2088" windowWidth="17640" windowHeight="9444" firstSheet="3" activeTab="5" xr2:uid="{B9AE4098-F0A1-4C76-B9D5-37F1BE2208A4}"/>
   </bookViews>
   <sheets>
     <sheet name="indoor_units" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="outdoor_units" sheetId="2" r:id="rId3"/>
     <sheet name="indoor_units_SA only" sheetId="3" r:id="rId4"/>
     <sheet name="outdoor_units_SA only" sheetId="4" r:id="rId5"/>
+    <sheet name="HRV" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3863" uniqueCount="653">
   <si>
     <t>資料型態</t>
   </si>
@@ -2439,6 +2440,82 @@
   </si>
   <si>
     <t>BHFP22P151</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全熱交換器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>循環風量(CMH)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM150HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM250HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM350HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM500HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM650HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM800HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM1000HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM1500HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAM2000HVLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PM2.5濾網</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尺寸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>278×551×810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>306×800×879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>338×832×973</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>387×1,012×1,110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>785×1,012×1,110</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2661,7 +2738,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2852,6 +2929,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -21801,4 +21887,328 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F35F01A9-3653-4C55-BE38-1F4E2BEE205E}">
+  <dimension ref="A2:M10"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="16.21875" customWidth="1"/>
+    <col min="3" max="4" width="16.21875" hidden="1" customWidth="1"/>
+    <col min="5" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="16.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>634</v>
+      </c>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>605</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="65" t="s">
+        <v>636</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="12">
+        <v>150</v>
+      </c>
+      <c r="F4" s="12">
+        <v>250</v>
+      </c>
+      <c r="G4" s="12">
+        <v>350</v>
+      </c>
+      <c r="H4" s="12">
+        <v>500</v>
+      </c>
+      <c r="I4" s="12">
+        <v>650</v>
+      </c>
+      <c r="J4" s="12">
+        <v>800</v>
+      </c>
+      <c r="K4" s="12">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="12">
+        <v>1500</v>
+      </c>
+      <c r="M4" s="12">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="65" t="s">
+        <v>646</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="12">
+        <f>0.03*2</f>
+        <v>0.06</v>
+      </c>
+      <c r="F7" s="12">
+        <f>0.03*2</f>
+        <v>0.06</v>
+      </c>
+      <c r="G7" s="12">
+        <f>0.06*2</f>
+        <v>0.12</v>
+      </c>
+      <c r="H7" s="12">
+        <f>0.1*2</f>
+        <v>0.2</v>
+      </c>
+      <c r="I7" s="12">
+        <f>0.17*2</f>
+        <v>0.34</v>
+      </c>
+      <c r="J7" s="12">
+        <f>0.19*2</f>
+        <v>0.38</v>
+      </c>
+      <c r="K7" s="12">
+        <f>0.19*2</f>
+        <v>0.38</v>
+      </c>
+      <c r="L7" s="12">
+        <f>0.19*4</f>
+        <v>0.76</v>
+      </c>
+      <c r="M7" s="12">
+        <f>0.19*4</f>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="65" t="s">
+        <v>647</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="66" t="s">
+        <v>552</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="49">
+        <v>50000</v>
+      </c>
+      <c r="F9" s="49">
+        <v>60000</v>
+      </c>
+      <c r="G9" s="49">
+        <v>70000</v>
+      </c>
+      <c r="H9" s="49">
+        <v>80000</v>
+      </c>
+      <c r="I9" s="49">
+        <v>50000</v>
+      </c>
+      <c r="J9" s="49">
+        <v>50000</v>
+      </c>
+      <c r="K9" s="49">
+        <v>50000</v>
+      </c>
+      <c r="L9" s="49">
+        <v>50000</v>
+      </c>
+      <c r="M9" s="49">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="24"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>